--- a/신고신저가_20260825.xlsx
+++ b/신고신저가_20260825.xlsx
@@ -33,7 +33,7 @@
     <numFmt numFmtId="164" formatCode="+0.00&quot;%&quot;;-0.00&quot;%&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +44,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
     <font>
       <color rgb="000000C0"/>
     </font>
@@ -76,15 +77,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
@@ -453,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -611,7 +616,84 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>💬 ■ 결론: 8월 24일 장을 하나로 꿰는 것은 AI 투자에 들어가는 돈의 값이 마침내 가격에 찍혔다는 점이다. 미 장기금리가 30년 5.27퍼센트까지 밀려 올라간 와중에 알리바바가 AI 투자 재원을 자기자본으로 조달하겠다고 밝히자, 그동안 AI 수요의 수혜자로 한데 묶여 있던 반도체와 전력이 미국·홍콩·중국에서 동시에 신저가를 냈다. 반대로 이익이 지금 눈에 보이는 은행과 금, 정유, 저가 소매로 돈이 옮겨갔다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>■ 美(8/24): 지수는 거의 제자리였지만 안에서는 하드웨어를 팔아 금융과 광산으로 갈아타는 하루였다. 다우가 오르는 동안 나스닥이 0.76퍼센트 내렸고, 그 대비가 신고신저에 그대로 찍혔다. 금융과 금·구리 광산에서 신고가가 쏟아진 반면 전자기술에서는 13종이 신저가로 밀렸다. 비자와 마스터카드가 나란히 3퍼센트 넘게 올라 신고가를 찍었는데, 목표가 상향에 트럼프 투자계좌의 6월 매수 공시가 겹쳤다. 유틸리티에서는 장중 신저가가 14종 나왔고, 텍사스 데이터센터 접속 감사에 걸린 발전사와 장기금리에 눌린 규제 전력회사가 함께 섞여 있다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>■ 日(8/24): 조용한 가운데 종합상사만 홀로 올라선 장이었다. 신저가가 한 종목도 없이 신고가만 아홉 종목 나왔고, 업종으로는 상사·도매가 가장 강했다. 이토추상사가 3000억엔 규모 자사주매입과 사상 최대 순이익의 여진을 타고 신고가를 이어갔다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>■ 홍콩(8/24): 알리바바의 증자 한 건이 시장 전체를 끌어내렸다. AI 투자 재원으로 102억달러를 할인 발행하겠다고 밝히자 주가가 9.8퍼센트 빠졌고, 항셍테크는 3.61퍼센트 하락해 52주 범위의 바닥권에 머물렀다. 희석 우려가 밸류체인으로 번지면서 톈수즈신과 화훙반도체가 나란히 신저가로 떨어졌다. 그 와중에 신고가 자리는 시노펙과 금광, 전력 같은 배당·실물 자산이 채웠다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>■ 中(8/24): 홍콩을 때린 것과 같은 힘이 반도체를 누르고 은행을 밀어 올렸다. 반도체 상장지수펀드가 3.1퍼센트 내리는 동안 은행은 1.5퍼센트 올랐다. 캄브리콘을 비롯한 AI칩 설계사들이 신저가로 떨어진 반면 중신은행은 장중 사상 최고가를 새로 썼다. 나머지 신고가도 실적을 낸 시노펙과 금값 최고치를 등에 업은 금광주에 몰렸다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>■ 체크: ① 30년 국채 금리가 5.3퍼센트 위에 자리를 잡는지 본다. 넘어서면 배당주와 고밸류 성장주가 같은 방향으로 한 번 더 눌린다. ② 알리바바에 이어 다른 중국 플랫폼들이 AI 투자 재원을 자기자본으로 조달하는지, 회사채로 가는지 확인한다. 조달 방식이 희석 우려가 어디까지 번질지를 정한다. ③ 텍사스 데이터센터 접속 감사 결과를 본다. AI 전력 수요가 언제 실적으로 들어오는지의 시점표다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>■ 배울점: 이날 미국 유틸리티에서 장중 신저가가 14종 나왔는데, 같은 신저가라도 안을 열면 두 갈래로 갈린다. 비스트라와 NRG 같은 도매 발전사는 데이터센터가 전기를 얼마나 사줄 것이냐에 이익이 통째로 걸린 회사라, 텍사스가 신규 접속을 멈추고 감사에 들어가자 팔 수 있는 전력량 자체가 뒤로 밀렸다. 이쪽은 이익의 Q가 깎인 것이다. 반면 넥스트에라나 엔터지 같은 규제 전력회사는 요금이 정해져 있어 당장의 이익은 그대로인데, 배당을 아주 멀리까지 받아야 하는 자산이라 30년 국채가 5.27퍼센트로 오르면 그 배당의 현재가치가 줄어든다. 이쪽은 이익이 아니라 멀티플이 깎인 것이다. 같은 금리 상승이 예대마진으로 먹고사는 은행에는 반대로 연료가 되어, 중신은행과 도이체방크가 같은 날 신고가를 냈다. 앞으로 어느 설명이 맞았는지는 텍사스 감사 결과가 발전사를, 30년 금리가 규제 전력회사를 각각 따로 채점해 알려준다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>■ 참고: 위 시장별 날짜는 각 시장의 현지 마감일이며, 미국 8월 24일 장은 한국시간 8월 25일 새벽 5시에 끝난 직전 세션이다. 지수 시트의 닛케이225와 코스피는 소스 지연으로 8월 21일 종가가 실려 있어 본문에서는 인용하지 않았고, 일본 신고신저 판정 자체는 8월 24일 장 기준이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>※ 60일 컬럼은 TradingView 3개월(약 63거래일) 고저가 기준. 신고/신저 판정: 당일 고가(저가)가 해당 기간 최고(최저)가 도달.</t>
         </is>
@@ -709,19 +791,19 @@
       <c r="C2" t="n">
         <v>7652.86</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="4" t="n">
         <v>-0.28</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="4" t="n">
         <v>-1.19</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="5" t="n">
         <v>3.25</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="5" t="n">
         <v>2.4</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" s="5" t="n">
         <v>11.79</v>
       </c>
       <c r="I2" t="n">
@@ -747,19 +829,19 @@
       <c r="C3" t="n">
         <v>25980.19</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="4" t="n">
         <v>-0.76</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="4" t="n">
         <v>-2.49</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="5" t="n">
         <v>4.02</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="4" t="n">
         <v>-1.38</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" s="5" t="n">
         <v>11.78</v>
       </c>
       <c r="I3" t="n">
@@ -785,19 +867,19 @@
       <c r="C4" t="n">
         <v>6912.95</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="5" t="n">
         <v>0.88</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="5" t="n">
         <v>1.46</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="5" t="n">
         <v>1.7</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="4" t="n">
         <v>-4.11</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" s="5" t="n">
         <v>64.04000000000001</v>
       </c>
       <c r="I4" t="n">
@@ -823,19 +905,19 @@
       <c r="C5" t="n">
         <v>66016.36</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="4" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="4" t="n">
         <v>-3.93</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="4" t="n">
         <v>-0.15</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" s="5" t="n">
         <v>4.23</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="5" t="n">
         <v>31.14</v>
       </c>
       <c r="I5" t="n">
@@ -861,19 +943,19 @@
       <c r="C6" t="n">
         <v>3882.01</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="4" t="n">
         <v>-0.59</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="4" t="n">
         <v>-2.53</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="5" t="n">
         <v>1.78</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="4" t="n">
         <v>-6.35</v>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="H6" s="4" t="n">
         <v>-2.19</v>
       </c>
       <c r="I6" t="n">
@@ -899,19 +981,19 @@
       <c r="C7" t="n">
         <v>4563.13</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="4" t="n">
         <v>-1.21</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="4" t="n">
         <v>-3.75</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="4" t="n">
         <v>-1.85</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="4" t="n">
         <v>-7.78</v>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="H7" s="4" t="n">
         <v>-1.44</v>
       </c>
       <c r="I7" t="n">
@@ -937,19 +1019,19 @@
       <c r="C8" t="n">
         <v>25517.33</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="4" t="n">
         <v>-1.89</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="5" t="n">
         <v>0.25</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" s="5" t="n">
         <v>2.22</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G8" s="4" t="n">
         <v>-0.35</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H8" s="4" t="n">
         <v>-0.44</v>
       </c>
       <c r="I8" t="n">
@@ -975,19 +1057,19 @@
       <c r="C9" t="n">
         <v>4594.04</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="4" t="n">
         <v>-3.61</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="4" t="n">
         <v>-3.93</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="4" t="n">
         <v>-0.77</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G9" s="4" t="n">
         <v>-5.66</v>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="H9" s="4" t="n">
         <v>-16.71</v>
       </c>
       <c r="I9" t="n">
@@ -1106,7 +1188,7 @@
       <c r="F2" t="n">
         <v>16</v>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1147,7 +1229,7 @@
       <c r="F3" t="n">
         <v>14</v>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1188,7 +1270,7 @@
       <c r="F4" t="n">
         <v>12</v>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1229,7 +1311,7 @@
       <c r="F5" t="n">
         <v>8</v>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1270,7 +1352,7 @@
       <c r="F6" t="n">
         <v>8</v>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1311,7 +1393,7 @@
       <c r="F7" t="n">
         <v>5</v>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1352,7 +1434,7 @@
       <c r="F8" t="n">
         <v>5</v>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1393,7 +1475,7 @@
       <c r="F9" t="n">
         <v>4</v>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1434,7 +1516,7 @@
       <c r="F10" t="n">
         <v>3</v>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1475,7 +1557,7 @@
       <c r="F11" t="n">
         <v>3</v>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1516,7 +1598,7 @@
       <c r="F12" t="n">
         <v>2</v>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1557,7 +1639,7 @@
       <c r="F13" t="n">
         <v>2</v>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1598,7 +1680,7 @@
       <c r="F14" t="n">
         <v>-1</v>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1639,7 +1721,7 @@
       <c r="F15" t="n">
         <v>-2</v>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1680,7 +1762,7 @@
       <c r="F16" t="n">
         <v>-5</v>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1721,7 +1803,7 @@
       <c r="F17" t="n">
         <v>-7</v>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1762,7 +1844,7 @@
       <c r="F18" t="n">
         <v>-13</v>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G18" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1803,7 +1885,7 @@
       <c r="F19" t="n">
         <v>-13</v>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1924,7 +2006,7 @@
       <c r="F22" t="n">
         <v>3</v>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1963,7 +2045,7 @@
       <c r="F23" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2002,7 +2084,7 @@
       <c r="F24" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2041,7 +2123,7 @@
       <c r="F25" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2080,7 +2162,7 @@
       <c r="F26" t="n">
         <v>1</v>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2121,7 +2203,7 @@
       <c r="F27" t="n">
         <v>1</v>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2160,7 +2242,7 @@
       <c r="F28" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="4" t="inlineStr">
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2677,7 +2759,7 @@
       <c r="F41" t="n">
         <v>6</v>
       </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="G41" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2718,7 +2800,7 @@
       <c r="F42" t="n">
         <v>4</v>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2757,7 +2839,7 @@
       <c r="F43" t="n">
         <v>2</v>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="G43" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2798,7 +2880,7 @@
       <c r="F44" t="n">
         <v>2</v>
       </c>
-      <c r="G44" s="4" t="inlineStr">
+      <c r="G44" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2837,7 +2919,7 @@
       <c r="F45" t="n">
         <v>1</v>
       </c>
-      <c r="G45" s="4" t="inlineStr">
+      <c r="G45" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2876,7 +2958,7 @@
       <c r="F46" t="n">
         <v>1</v>
       </c>
-      <c r="G46" s="4" t="inlineStr">
+      <c r="G46" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2915,7 +2997,7 @@
       <c r="F47" t="n">
         <v>-1</v>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="G47" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2954,7 +3036,7 @@
       <c r="F48" t="n">
         <v>-1</v>
       </c>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="G48" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2995,7 +3077,7 @@
       <c r="F49" t="n">
         <v>-1</v>
       </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="G49" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3036,7 +3118,7 @@
       <c r="F50" t="n">
         <v>-2</v>
       </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="G50" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3393,7 +3475,7 @@
       <c r="F59" t="n">
         <v>4</v>
       </c>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="G59" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3434,7 +3516,7 @@
       <c r="F60" t="n">
         <v>2</v>
       </c>
-      <c r="G60" s="4" t="inlineStr">
+      <c r="G60" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3475,7 +3557,7 @@
       <c r="F61" t="n">
         <v>1</v>
       </c>
-      <c r="G61" s="4" t="inlineStr">
+      <c r="G61" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3514,7 +3596,7 @@
       <c r="F62" t="n">
         <v>1</v>
       </c>
-      <c r="G62" s="4" t="inlineStr">
+      <c r="G62" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3553,7 +3635,7 @@
       <c r="F63" t="n">
         <v>1</v>
       </c>
-      <c r="G63" s="4" t="inlineStr">
+      <c r="G63" s="6" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -3592,7 +3674,7 @@
       <c r="F64" t="n">
         <v>-1</v>
       </c>
-      <c r="G64" s="5" t="inlineStr">
+      <c r="G64" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3631,7 +3713,7 @@
       <c r="F65" t="n">
         <v>-1</v>
       </c>
-      <c r="G65" s="5" t="inlineStr">
+      <c r="G65" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3670,7 +3752,7 @@
       <c r="F66" t="n">
         <v>-1</v>
       </c>
-      <c r="G66" s="5" t="inlineStr">
+      <c r="G66" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3711,7 +3793,7 @@
       <c r="F67" t="n">
         <v>-1</v>
       </c>
-      <c r="G67" s="5" t="inlineStr">
+      <c r="G67" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3752,7 +3834,7 @@
       <c r="F68" t="n">
         <v>-1</v>
       </c>
-      <c r="G68" s="5" t="inlineStr">
+      <c r="G68" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3793,7 +3875,7 @@
       <c r="F69" t="n">
         <v>-5</v>
       </c>
-      <c r="G69" s="5" t="inlineStr">
+      <c r="G69" s="7" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -4101,30 +4183,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U47"/>
+  <dimension ref="A1:V47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="95" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="6" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="6" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="6" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+    <col width="8" customWidth="1" min="19" max="19"/>
+    <col width="6" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4145,90 +4228,95 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>코멘트</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>1D</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>1주</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>YTD26</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>순위26</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>YTD25</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>순위25</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>YTD24</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>순위24</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>YTD23</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>순위23</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>YTD22</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>순위22</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>YTD21</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>순위21</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>YTD20</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>순위20</t>
         </is>
@@ -4250,58 +4338,63 @@
           <t>테크</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>1.8퍼센트 하락으로 11개 중 최약. 전자기술 13종 신저가로 하드웨어가 짐. 소프트웨어는 신고가 20종으로 정반대</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="n">
         <v>-1.8</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="F2" s="9" t="n">
         <v>-5.4</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="G2" s="9" t="n">
         <v>2.4</v>
       </c>
-      <c r="G2" s="6" t="n">
+      <c r="H2" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="H2" s="6" t="n">
+      <c r="I2" s="9" t="n">
         <v>25.4</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>2</v>
       </c>
-      <c r="J2" s="6" t="n">
+      <c r="K2" s="9" t="n">
         <v>24.6</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" s="6" t="n">
+      <c r="M2" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>5</v>
       </c>
-      <c r="N2" s="6" t="n">
+      <c r="O2" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" s="6" t="n">
+      <c r="Q2" s="9" t="n">
         <v>-27.7</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>9</v>
       </c>
-      <c r="R2" s="6" t="n">
+      <c r="S2" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>4</v>
       </c>
-      <c r="T2" s="6" t="n">
+      <c r="U2" s="9" t="n">
         <v>43.6</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4321,58 +4414,63 @@
           <t>헬스케어</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>보합이나 3개월 17.1퍼센트로 압도적 1위. 금리·AI와 무관한 이익이 피난처 역할</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="F3" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="G3" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="H3" s="9" t="n">
         <v>17.1</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="I3" s="9" t="n">
         <v>13.8</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>7</v>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="K3" s="9" t="n">
         <v>14.5</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>6</v>
       </c>
-      <c r="L3" s="6" t="n">
+      <c r="M3" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>10</v>
       </c>
-      <c r="N3" s="6" t="n">
+      <c r="O3" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>8</v>
       </c>
-      <c r="P3" s="6" t="n">
+      <c r="Q3" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>4</v>
       </c>
-      <c r="R3" s="6" t="n">
+      <c r="S3" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>7</v>
       </c>
-      <c r="T3" s="6" t="n">
+      <c r="U3" s="9" t="n">
         <v>13.3</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4392,58 +4490,63 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>1.3퍼센트 상승, 신고가 14종으로 미국 최다 강세. 비자·마스터카드 3퍼센트대 급등이 견인</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="F4" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="G4" s="9" t="n">
         <v>3.4</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="H4" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="I4" s="9" t="n">
         <v>7.2</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="K4" s="9" t="n">
         <v>14.9</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>5</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="M4" s="9" t="n">
         <v>30.6</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>2</v>
       </c>
-      <c r="N4" s="6" t="n">
+      <c r="O4" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>7</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="Q4" s="9" t="n">
         <v>-10.6</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>6</v>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="S4" s="9" t="n">
         <v>34.8</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>3</v>
       </c>
-      <c r="T4" s="6" t="n">
+      <c r="U4" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4463,58 +4566,63 @@
           <t>경기소비재</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>0.2퍼센트 강보합이나 저가 소매에서 신고가 집중. 달러트리·파이브빌로우 등 소비 하향이동 수혜 추정</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="F5" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="G5" s="9" t="n">
         <v>8.1</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="H5" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="I5" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>10</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="K5" s="9" t="n">
         <v>7.4</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>9</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="M5" s="9" t="n">
         <v>26.5</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>3</v>
       </c>
-      <c r="N5" s="6" t="n">
+      <c r="O5" s="9" t="n">
         <v>39.6</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>3</v>
       </c>
-      <c r="P5" s="6" t="n">
+      <c r="Q5" s="9" t="n">
         <v>-36.3</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>10</v>
       </c>
-      <c r="R5" s="6" t="n">
+      <c r="S5" s="9" t="n">
         <v>27.9</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>5</v>
       </c>
-      <c r="T5" s="6" t="n">
+      <c r="U5" s="9" t="n">
         <v>29.6</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4534,58 +4642,63 @@
           <t>커뮤니케이션</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>0.8퍼센트 상승. YTD 마이너스 4퍼센트로 연간 최하위지만 당일은 기술주 회피의 반사이익</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="F6" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="G6" s="9" t="n">
         <v>5.7</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="H6" s="9" t="n">
         <v>-2.5</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="I6" s="9" t="n">
         <v>-4</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>11</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="K6" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="M6" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>1</v>
       </c>
-      <c r="N6" s="6" t="n">
+      <c r="O6" s="9" t="n">
         <v>52.8</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>2</v>
       </c>
-      <c r="P6" s="6" t="n">
+      <c r="Q6" s="9" t="n">
         <v>-37.6</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>11</v>
       </c>
-      <c r="R6" s="6" t="n">
+      <c r="S6" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>11</v>
       </c>
-      <c r="T6" s="6" t="n">
+      <c r="U6" s="9" t="n">
         <v>26.9</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4605,58 +4718,63 @@
           <t>산업재</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>0.7퍼센트 하락, 주간 3.9퍼센트 약세. 화물운송 신저가와 전력설비 되감김이 겹침</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="F7" s="9" t="n">
         <v>-3.9</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="G7" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="H7" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="I7" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>4</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="K7" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>3</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="M7" s="9" t="n">
         <v>17.3</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>6</v>
       </c>
-      <c r="N7" s="6" t="n">
+      <c r="O7" s="9" t="n">
         <v>18.1</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>4</v>
       </c>
-      <c r="P7" s="6" t="n">
+      <c r="Q7" s="9" t="n">
         <v>-5.6</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>5</v>
       </c>
-      <c r="R7" s="6" t="n">
+      <c r="S7" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>8</v>
       </c>
-      <c r="T7" s="6" t="n">
+      <c r="U7" s="9" t="n">
         <v>10.9</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4676,58 +4794,63 @@
           <t>필수소비재</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>1.7퍼센트로 당일 최강. 장기금리 상승 국면에서 방어주로 자금 유입</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
         <v>1.7</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="F8" s="9" t="n">
         <v>3.3</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="G8" s="9" t="n">
         <v>3.9</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="H8" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="I8" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>6</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="K8" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>11</v>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="M8" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>7</v>
       </c>
-      <c r="N8" s="6" t="n">
+      <c r="O8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>10</v>
       </c>
-      <c r="P8" s="6" t="n">
+      <c r="Q8" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>3</v>
       </c>
-      <c r="R8" s="6" t="n">
+      <c r="S8" s="9" t="n">
         <v>17.2</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>10</v>
       </c>
-      <c r="T8" s="6" t="n">
+      <c r="U8" s="9" t="n">
         <v>10.1</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4747,58 +4870,63 @@
           <t>에너지</t>
         </is>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>0.8퍼센트 하락했으나 YTD 43.1퍼센트로 연간 1위 유지. 중동 리스크 프리미엄이 바탕</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="F9" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="G9" s="9" t="n">
         <v>5.9</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="H9" s="9" t="n">
         <v>6.9</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="I9" s="9" t="n">
         <v>43.1</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="K9" s="9" t="n">
         <v>7.9</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>8</v>
       </c>
-      <c r="L9" s="6" t="n">
+      <c r="M9" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>8</v>
       </c>
-      <c r="N9" s="6" t="n">
+      <c r="O9" s="9" t="n">
         <v>-0.6</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>9</v>
       </c>
-      <c r="P9" s="6" t="n">
+      <c r="Q9" s="9" t="n">
         <v>64.3</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>1</v>
       </c>
-      <c r="R9" s="6" t="n">
+      <c r="S9" s="9" t="n">
         <v>53.3</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="T9" s="6" t="n">
+      <c r="U9" s="9" t="n">
         <v>-32.7</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>11</v>
       </c>
     </row>
@@ -4818,58 +4946,63 @@
           <t>유틸리티</t>
         </is>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>1.1퍼센트 반등 마감이나 장중 신저가 14종. 텍사스 접속 감사와 30년 금리에 1개월 6.6퍼센트 하락</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="F10" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="G10" s="9" t="n">
         <v>-6.6</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="H10" s="9" t="n">
         <v>-4.1</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="I10" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>9</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="K10" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>4</v>
       </c>
-      <c r="L10" s="6" t="n">
+      <c r="M10" s="9" t="n">
         <v>23.3</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>4</v>
       </c>
-      <c r="N10" s="6" t="n">
+      <c r="O10" s="9" t="n">
         <v>-7.2</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>11</v>
       </c>
-      <c r="P10" s="6" t="n">
+      <c r="Q10" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>2</v>
       </c>
-      <c r="R10" s="6" t="n">
+      <c r="S10" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>9</v>
       </c>
-      <c r="T10" s="6" t="n">
+      <c r="U10" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4889,58 +5022,63 @@
           <t>소재</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>0.1퍼센트 보합이나 금·구리 광산 12종이 신고가. 금값 사상최고가 실질 동력</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="F11" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="G11" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="H11" s="9" t="n">
         <v>6.9</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="I11" s="9" t="n">
         <v>19.1</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>3</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="K11" s="9" t="n">
         <v>9.9</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>7</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="M11" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>11</v>
       </c>
-      <c r="N11" s="6" t="n">
+      <c r="O11" s="9" t="n">
         <v>12.5</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>5</v>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="Q11" s="9" t="n">
         <v>-12.3</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>7</v>
       </c>
-      <c r="R11" s="6" t="n">
+      <c r="S11" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>6</v>
       </c>
-      <c r="T11" s="6" t="n">
+      <c r="U11" s="9" t="n">
         <v>20.5</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4960,58 +5098,63 @@
           <t>리츠</t>
         </is>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>0.6퍼센트 상승. 장기금리 부담에도 당일은 방어주 수급에 동참</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="F12" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="G12" s="9" t="n">
         <v>-1.3</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="H12" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="I12" s="9" t="n">
         <v>14.1</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>5</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="K12" s="9" t="n">
         <v>2.6</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>10</v>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="M12" s="9" t="n">
         <v>5.1</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>9</v>
       </c>
-      <c r="N12" s="6" t="n">
+      <c r="O12" s="9" t="n">
         <v>12.4</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>6</v>
       </c>
-      <c r="P12" s="6" t="n">
+      <c r="Q12" s="9" t="n">
         <v>-26.2</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>8</v>
       </c>
-      <c r="R12" s="6" t="n">
+      <c r="S12" s="9" t="n">
         <v>46.1</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>2</v>
       </c>
-      <c r="T12" s="6" t="n">
+      <c r="U12" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>10</v>
       </c>
     </row>
@@ -5031,58 +5174,59 @@
           <t>식품</t>
         </is>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="8" t="inlineStr"/>
+      <c r="E13" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="F13" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="G13" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="H13" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="I13" s="9" t="n">
         <v>21.9</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>5</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="K13" s="9" t="n">
         <v>11.8</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>15</v>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="M13" s="9" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>14</v>
       </c>
-      <c r="N13" s="6" t="n">
+      <c r="O13" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>13</v>
       </c>
-      <c r="P13" s="6" t="n">
+      <c r="Q13" s="9" t="n">
         <v>6.4</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>10</v>
       </c>
-      <c r="R13" s="6" t="n">
+      <c r="S13" s="9" t="n">
         <v>5.6</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>11</v>
       </c>
-      <c r="T13" s="6" t="n">
+      <c r="U13" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>9</v>
       </c>
     </row>
@@ -5102,58 +5246,59 @@
           <t>에너지자원</t>
         </is>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="8" t="inlineStr"/>
+      <c r="E14" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="F14" s="9" t="n">
         <v>3.1</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="G14" s="9" t="n">
         <v>3.7</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="H14" s="9" t="n">
         <v>6.1</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="I14" s="9" t="n">
         <v>21.9</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>5</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="K14" s="9" t="n">
         <v>41.4</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>6</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="M14" s="9" t="n">
         <v>29.9</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>3</v>
       </c>
-      <c r="N14" s="6" t="n">
+      <c r="O14" s="9" t="n">
         <v>37.2</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>3</v>
       </c>
-      <c r="P14" s="6" t="n">
+      <c r="Q14" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>2</v>
       </c>
-      <c r="R14" s="6" t="n">
+      <c r="S14" s="9" t="n">
         <v>39.3</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="T14" s="6" t="n">
+      <c r="U14" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>17</v>
       </c>
     </row>
@@ -5173,58 +5318,59 @@
           <t>건설·자재</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="8" t="inlineStr"/>
+      <c r="E15" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="F15" s="9" t="n">
         <v>-3.3</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="G15" s="9" t="n">
         <v>-4.5</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="H15" s="9" t="n">
         <v>-5.5</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="I15" s="9" t="n">
         <v>6.1</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>14</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="K15" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>3</v>
       </c>
-      <c r="L15" s="6" t="n">
+      <c r="M15" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>6</v>
       </c>
-      <c r="N15" s="6" t="n">
+      <c r="O15" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>9</v>
       </c>
-      <c r="P15" s="6" t="n">
+      <c r="Q15" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>12</v>
       </c>
-      <c r="R15" s="6" t="n">
+      <c r="S15" s="9" t="n">
         <v>12.6</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>8</v>
       </c>
-      <c r="T15" s="6" t="n">
+      <c r="U15" s="9" t="n">
         <v>-6.1</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>11</v>
       </c>
     </row>
@@ -5244,58 +5390,59 @@
           <t>소재·화학</t>
         </is>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="8" t="inlineStr"/>
+      <c r="E16" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="F16" s="9" t="n">
         <v>-3.1</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="G16" s="9" t="n">
         <v>-3.5</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="H16" s="9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="I16" s="9" t="n">
         <v>20.3</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>7</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="K16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>17</v>
       </c>
-      <c r="L16" s="6" t="n">
+      <c r="M16" s="9" t="n">
         <v>3.9</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>16</v>
       </c>
-      <c r="N16" s="6" t="n">
+      <c r="O16" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>12</v>
       </c>
-      <c r="P16" s="6" t="n">
+      <c r="Q16" s="9" t="n">
         <v>-9.4</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>14</v>
       </c>
-      <c r="R16" s="6" t="n">
+      <c r="S16" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>14</v>
       </c>
-      <c r="T16" s="6" t="n">
+      <c r="U16" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5315,58 +5462,59 @@
           <t>의약품</t>
         </is>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="8" t="inlineStr"/>
+      <c r="E17" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="F17" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="G17" s="9" t="n">
         <v>5.9</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="H17" s="9" t="n">
         <v>4.9</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="I17" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>12</v>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="K17" s="9" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>16</v>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="M17" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>13</v>
       </c>
-      <c r="N17" s="6" t="n">
+      <c r="O17" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>17</v>
       </c>
-      <c r="P17" s="6" t="n">
+      <c r="Q17" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>4</v>
       </c>
-      <c r="R17" s="6" t="n">
+      <c r="S17" s="9" t="n">
         <v>-8.4</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>17</v>
       </c>
-      <c r="T17" s="6" t="n">
+      <c r="U17" s="9" t="n">
         <v>4.6</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5386,58 +5534,59 @@
           <t>자동차·운송기기</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="8" t="inlineStr"/>
+      <c r="E18" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="F18" s="9" t="n">
         <v>2.1</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="G18" s="9" t="n">
         <v>5.3</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="H18" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="I18" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>16</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="K18" s="9" t="n">
         <v>13.5</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>14</v>
       </c>
-      <c r="L18" s="6" t="n">
+      <c r="M18" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>11</v>
       </c>
-      <c r="N18" s="6" t="n">
+      <c r="O18" s="9" t="n">
         <v>40.5</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>2</v>
       </c>
-      <c r="P18" s="6" t="n">
+      <c r="Q18" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>16</v>
       </c>
-      <c r="R18" s="6" t="n">
+      <c r="S18" s="9" t="n">
         <v>27.8</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>3</v>
       </c>
-      <c r="T18" s="6" t="n">
+      <c r="U18" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>8</v>
       </c>
     </row>
@@ -5457,58 +5606,59 @@
           <t>철강·비철</t>
         </is>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="8" t="inlineStr"/>
+      <c r="E19" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="F19" s="9" t="n">
         <v>-7.9</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="G19" s="9" t="n">
         <v>2.8</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="H19" s="9" t="n">
         <v>-13.9</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="I19" s="9" t="n">
         <v>46.7</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="K19" s="9" t="n">
         <v>68.8</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="L19" s="6" t="n">
+      <c r="M19" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>8</v>
       </c>
-      <c r="N19" s="6" t="n">
+      <c r="O19" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>4</v>
       </c>
-      <c r="P19" s="6" t="n">
+      <c r="Q19" s="9" t="n">
         <v>16.1</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>5</v>
       </c>
-      <c r="R19" s="6" t="n">
+      <c r="S19" s="9" t="n">
         <v>20.8</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>7</v>
       </c>
-      <c r="T19" s="6" t="n">
+      <c r="U19" s="9" t="n">
         <v>-8.6</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5528,58 +5678,59 @@
           <t>기계</t>
         </is>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="8" t="inlineStr"/>
+      <c r="E20" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="F20" s="9" t="n">
         <v>-6.4</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="G20" s="9" t="n">
         <v>-4.1</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="H20" s="9" t="n">
         <v>-3.3</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="I20" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>9</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="K20" s="9" t="n">
         <v>31.1</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>8</v>
       </c>
-      <c r="L20" s="6" t="n">
+      <c r="M20" s="9" t="n">
         <v>22.3</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>5</v>
       </c>
-      <c r="N20" s="6" t="n">
+      <c r="O20" s="9" t="n">
         <v>33.9</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>6</v>
       </c>
-      <c r="P20" s="6" t="n">
+      <c r="Q20" s="9" t="n">
         <v>-9.9</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>15</v>
       </c>
-      <c r="R20" s="6" t="n">
+      <c r="S20" s="9" t="n">
         <v>7.5</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>9</v>
       </c>
-      <c r="T20" s="6" t="n">
+      <c r="U20" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5599,58 +5750,59 @@
           <t>전기·정밀</t>
         </is>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="8" t="inlineStr"/>
+      <c r="E21" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="F21" s="9" t="n">
         <v>-7.1</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="G21" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="H21" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="I21" s="9" t="n">
         <v>31.2</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>3</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="K21" s="9" t="n">
         <v>27.5</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>9</v>
       </c>
-      <c r="L21" s="6" t="n">
+      <c r="M21" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>10</v>
       </c>
-      <c r="N21" s="6" t="n">
+      <c r="O21" s="9" t="n">
         <v>33.7</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>7</v>
       </c>
-      <c r="P21" s="6" t="n">
+      <c r="Q21" s="9" t="n">
         <v>-23</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>17</v>
       </c>
-      <c r="R21" s="6" t="n">
+      <c r="S21" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>5</v>
       </c>
-      <c r="T21" s="6" t="n">
+      <c r="U21" s="9" t="n">
         <v>26.2</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5670,58 +5822,59 @@
           <t>정보통신·서비스</t>
         </is>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="8" t="inlineStr"/>
+      <c r="E22" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="F22" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="G22" s="9" t="n">
         <v>7.6</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="H22" s="9" t="n">
         <v>10.2</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="I22" s="9" t="n">
         <v>12.9</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>10</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="K22" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>13</v>
       </c>
-      <c r="L22" s="6" t="n">
+      <c r="M22" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>7</v>
       </c>
-      <c r="N22" s="6" t="n">
+      <c r="O22" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>15</v>
       </c>
-      <c r="P22" s="6" t="n">
+      <c r="Q22" s="9" t="n">
         <v>-5.9</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>13</v>
       </c>
-      <c r="R22" s="6" t="n">
+      <c r="S22" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>13</v>
       </c>
-      <c r="T22" s="6" t="n">
+      <c r="U22" s="9" t="n">
         <v>21.9</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5741,58 +5894,59 @@
           <t>전력·가스</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="8" t="inlineStr"/>
+      <c r="E23" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="F23" s="9" t="n">
         <v>4.1</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="G23" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="H23" s="9" t="n">
         <v>4.9</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="I23" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>13</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="K23" s="9" t="n">
         <v>37.4</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>7</v>
       </c>
-      <c r="L23" s="6" t="n">
+      <c r="M23" s="9" t="n">
         <v>6.3</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>15</v>
       </c>
-      <c r="N23" s="6" t="n">
+      <c r="O23" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>4</v>
       </c>
-      <c r="P23" s="6" t="n">
+      <c r="Q23" s="9" t="n">
         <v>13.2</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>7</v>
       </c>
-      <c r="R23" s="6" t="n">
+      <c r="S23" s="9" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>16</v>
       </c>
-      <c r="T23" s="6" t="n">
+      <c r="U23" s="9" t="n">
         <v>-10.7</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>13</v>
       </c>
     </row>
@@ -5812,58 +5966,59 @@
           <t>운수·물류</t>
         </is>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="8" t="inlineStr"/>
+      <c r="E24" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="F24" s="9" t="n">
         <v>3.2</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="G24" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="H24" s="9" t="n">
         <v>11.2</v>
       </c>
-      <c r="H24" s="6" t="n">
+      <c r="I24" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>11</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="K24" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>11</v>
       </c>
-      <c r="L24" s="6" t="n">
+      <c r="M24" s="9" t="n">
         <v>-0</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>17</v>
       </c>
-      <c r="N24" s="6" t="n">
+      <c r="O24" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>14</v>
       </c>
-      <c r="P24" s="6" t="n">
+      <c r="Q24" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>8</v>
       </c>
-      <c r="R24" s="6" t="n">
+      <c r="S24" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>12</v>
       </c>
-      <c r="T24" s="6" t="n">
+      <c r="U24" s="9" t="n">
         <v>-17.1</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>16</v>
       </c>
     </row>
@@ -5883,58 +6038,59 @@
           <t>상사·도매</t>
         </is>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D25" s="8" t="inlineStr"/>
+      <c r="E25" s="9" t="n">
         <v>1.4</v>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="F25" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="G25" s="9" t="n">
         <v>2.4</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="H25" s="9" t="n">
         <v>-1.8</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="I25" s="9" t="n">
         <v>19.2</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>8</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="K25" s="9" t="n">
         <v>41.5</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>5</v>
       </c>
-      <c r="L25" s="6" t="n">
+      <c r="M25" s="9" t="n">
         <v>20.1</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>9</v>
       </c>
-      <c r="N25" s="6" t="n">
+      <c r="O25" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>1</v>
       </c>
-      <c r="P25" s="6" t="n">
+      <c r="Q25" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>3</v>
       </c>
-      <c r="R25" s="6" t="n">
+      <c r="S25" s="9" t="n">
         <v>29.2</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>2</v>
       </c>
-      <c r="T25" s="6" t="n">
+      <c r="U25" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5954,58 +6110,59 @@
           <t>소매</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D26" s="8" t="inlineStr"/>
+      <c r="E26" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="F26" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="G26" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="H26" s="9" t="n">
         <v>7.3</v>
       </c>
-      <c r="H26" s="6" t="n">
+      <c r="I26" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>15</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="K26" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>12</v>
       </c>
-      <c r="L26" s="6" t="n">
+      <c r="M26" s="9" t="n">
         <v>23.4</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>4</v>
       </c>
-      <c r="N26" s="6" t="n">
+      <c r="O26" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>16</v>
       </c>
-      <c r="P26" s="6" t="n">
+      <c r="Q26" s="9" t="n">
         <v>10.2</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>9</v>
       </c>
-      <c r="R26" s="6" t="n">
+      <c r="S26" s="9" t="n">
         <v>-4.4</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>15</v>
       </c>
-      <c r="T26" s="6" t="n">
+      <c r="U26" s="9" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6025,58 +6182,59 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="8" t="inlineStr"/>
+      <c r="E27" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="F27" s="9" t="n">
         <v>-4.2</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="G27" s="9" t="n">
         <v>-5.3</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="H27" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="I27" s="9" t="n">
         <v>43.3</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>2</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="K27" s="9" t="n">
         <v>44.8</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="L27" s="6" t="n">
+      <c r="M27" s="9" t="n">
         <v>50.4</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="6" t="n">
+      <c r="O27" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>8</v>
       </c>
-      <c r="P27" s="6" t="n">
+      <c r="Q27" s="9" t="n">
         <v>38.3</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>1</v>
       </c>
-      <c r="R27" s="6" t="n">
+      <c r="S27" s="9" t="n">
         <v>26.7</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>4</v>
       </c>
-      <c r="T27" s="6" t="n">
+      <c r="U27" s="9" t="n">
         <v>-16.3</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>15</v>
       </c>
     </row>
@@ -6096,58 +6254,59 @@
           <t>금융(은행외)</t>
         </is>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="8" t="inlineStr"/>
+      <c r="E28" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E28" s="6" t="n">
+      <c r="F28" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="F28" s="6" t="n">
+      <c r="G28" s="9" t="n">
         <v>-3.3</v>
       </c>
-      <c r="G28" s="6" t="n">
+      <c r="H28" s="9" t="n">
         <v>7.9</v>
       </c>
-      <c r="H28" s="6" t="n">
+      <c r="I28" s="9" t="n">
         <v>25.8</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>4</v>
       </c>
-      <c r="J28" s="6" t="n">
+      <c r="K28" s="9" t="n">
         <v>21.4</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>10</v>
       </c>
-      <c r="L28" s="6" t="n">
+      <c r="M28" s="9" t="n">
         <v>49</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>2</v>
       </c>
-      <c r="N28" s="6" t="n">
+      <c r="O28" s="9" t="n">
         <v>27.2</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>10</v>
       </c>
-      <c r="P28" s="6" t="n">
+      <c r="Q28" s="9" t="n">
         <v>13.7</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>6</v>
       </c>
-      <c r="R28" s="6" t="n">
+      <c r="S28" s="9" t="n">
         <v>22.6</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>6</v>
       </c>
-      <c r="T28" s="6" t="n">
+      <c r="U28" s="9" t="n">
         <v>-3.6</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>10</v>
       </c>
     </row>
@@ -6167,58 +6326,59 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="8" t="inlineStr"/>
+      <c r="E29" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="F29" s="9" t="n">
         <v>1.8</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="G29" s="9" t="n">
         <v>-3.2</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="H29" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="H29" s="6" t="n">
+      <c r="I29" s="9" t="n">
         <v>-4.9</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>17</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="K29" s="9" t="n">
         <v>41.6</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>4</v>
       </c>
-      <c r="L29" s="6" t="n">
+      <c r="M29" s="9" t="n">
         <v>13.9</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>12</v>
       </c>
-      <c r="N29" s="6" t="n">
+      <c r="O29" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>11</v>
       </c>
-      <c r="P29" s="6" t="n">
+      <c r="Q29" s="9" t="n">
         <v>4.4</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>11</v>
       </c>
-      <c r="R29" s="6" t="n">
+      <c r="S29" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>10</v>
       </c>
-      <c r="T29" s="6" t="n">
+      <c r="U29" s="9" t="n">
         <v>-13.3</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>14</v>
       </c>
     </row>
@@ -6238,58 +6398,59 @@
           <t>항셍지수</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D30" s="8" t="inlineStr"/>
+      <c r="E30" s="9" t="n">
         <v>-2</v>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="F30" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="G30" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="H30" s="9" t="n">
         <v>0.7</v>
       </c>
-      <c r="H30" s="6" t="n">
+      <c r="I30" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="K30" s="9" t="n">
         <v>27.4</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="L30" s="6" t="n">
+      <c r="M30" s="9" t="n">
         <v>17.9</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>3</v>
       </c>
-      <c r="N30" s="6" t="n">
+      <c r="O30" s="9" t="n">
         <v>-13.7</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>2</v>
       </c>
-      <c r="P30" s="6" t="n">
+      <c r="Q30" s="9" t="n">
         <v>-15.3</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>1</v>
       </c>
-      <c r="R30" s="6" t="n">
+      <c r="S30" s="9" t="n">
         <v>-14.2</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>1</v>
       </c>
-      <c r="T30" s="6" t="n">
+      <c r="U30" s="9" t="n">
         <v>-3.7</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6309,58 +6470,59 @@
           <t>H주(중국기업)</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="8" t="inlineStr"/>
+      <c r="E31" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="F31" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="G31" s="9" t="n">
         <v>2.3</v>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="H31" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="H31" s="6" t="n">
+      <c r="I31" s="9" t="n">
         <v>-4.6</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>2</v>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="K31" s="9" t="n">
         <v>22.9</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>2</v>
       </c>
-      <c r="L31" s="6" t="n">
+      <c r="M31" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="6" t="n">
+      <c r="O31" s="9" t="n">
         <v>-14.1</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>3</v>
       </c>
-      <c r="P31" s="6" t="n">
+      <c r="Q31" s="9" t="n">
         <v>-18.6</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>2</v>
       </c>
-      <c r="R31" s="6" t="n">
+      <c r="S31" s="9" t="n">
         <v>-23.2</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>2</v>
       </c>
-      <c r="T31" s="6" t="n">
+      <c r="U31" s="9" t="n">
         <v>-4.1</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6380,56 +6542,57 @@
           <t>항셍테크</t>
         </is>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D32" s="8" t="inlineStr"/>
+      <c r="E32" s="9" t="n">
         <v>-3.7</v>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="F32" s="9" t="n">
         <v>-4.3</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="G32" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="H32" s="9" t="n">
         <v>-5.5</v>
       </c>
-      <c r="H32" s="6" t="n">
+      <c r="I32" s="9" t="n">
         <v>-16.6</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>3</v>
       </c>
-      <c r="J32" s="6" t="n">
+      <c r="K32" s="9" t="n">
         <v>22.7</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>3</v>
       </c>
-      <c r="L32" s="6" t="n">
+      <c r="M32" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>2</v>
       </c>
-      <c r="N32" s="6" t="n">
+      <c r="O32" s="9" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>1</v>
       </c>
-      <c r="P32" s="6" t="n">
+      <c r="Q32" s="9" t="n">
         <v>-27.4</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>3</v>
       </c>
-      <c r="R32" s="6" t="n">
+      <c r="S32" s="9" t="n">
         <v>-32.9</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>3</v>
       </c>
-      <c r="T32" s="6" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+      <c r="U32" s="9" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6447,58 +6610,63 @@
           <t>반도체</t>
         </is>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>3.1퍼센트 급락, 주간 10.8퍼센트로 A주 최약. 알리바바 증자發 AI 자금조달 우려에 캄브리콘 등 신저가</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
         <v>-3.1</v>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="F33" s="9" t="n">
         <v>-10.8</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="G33" s="9" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="H33" s="9" t="n">
         <v>-13</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="I33" s="9" t="n">
         <v>38</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="K33" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>5</v>
       </c>
-      <c r="L33" s="6" t="n">
+      <c r="M33" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>3</v>
       </c>
-      <c r="N33" s="6" t="n">
+      <c r="O33" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>4</v>
       </c>
-      <c r="P33" s="6" t="n">
+      <c r="Q33" s="9" t="n">
         <v>-36.6</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>12</v>
       </c>
-      <c r="R33" s="6" t="n">
+      <c r="S33" s="9" t="n">
         <v>23.8</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>4</v>
       </c>
-      <c r="T33" s="6" t="n">
+      <c r="U33" s="9" t="n">
         <v>46.6</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6518,58 +6686,63 @@
           <t>테크(科技)</t>
         </is>
       </c>
-      <c r="D34" s="6" t="n">
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>3.4퍼센트 하락. 기술주 전반이 홍콩발 희석 우려에 동반 조정</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
         <v>-3.4</v>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="F34" s="9" t="n">
         <v>-10.2</v>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="G34" s="9" t="n">
         <v>-6.8</v>
       </c>
-      <c r="G34" s="6" t="n">
+      <c r="H34" s="9" t="n">
         <v>-13.6</v>
       </c>
-      <c r="H34" s="6" t="n">
+      <c r="I34" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>3</v>
       </c>
-      <c r="J34" s="6" t="n">
+      <c r="K34" s="9" t="n">
         <v>52.1</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>4</v>
       </c>
-      <c r="L34" s="6" t="n">
+      <c r="M34" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>5</v>
       </c>
-      <c r="N34" s="6" t="n">
+      <c r="O34" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P34" t="n">
         <v>3</v>
       </c>
-      <c r="P34" s="6" t="n">
+      <c r="Q34" s="9" t="n">
         <v>-34</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="R34" t="n">
         <v>11</v>
       </c>
-      <c r="R34" s="6" t="n">
+      <c r="S34" s="9" t="n">
         <v>-2.8</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T34" t="n">
         <v>8</v>
       </c>
-      <c r="T34" s="6" t="n">
+      <c r="U34" s="9" t="n">
         <v>46.1</v>
       </c>
-      <c r="U34" t="n">
+      <c r="V34" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6589,58 +6762,63 @@
           <t>5G통신</t>
         </is>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>4.5퍼센트로 13개 중 최대 낙폭. 3개월 16.9퍼센트 하락으로 AI 통신 인프라 되감김이 가장 깊음</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n">
         <v>-4.5</v>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="F35" s="9" t="n">
         <v>-10.2</v>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="G35" s="9" t="n">
         <v>-2.3</v>
       </c>
-      <c r="G35" s="6" t="n">
+      <c r="H35" s="9" t="n">
         <v>-16.9</v>
       </c>
-      <c r="H35" s="6" t="n">
+      <c r="I35" s="9" t="n">
         <v>32.1</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>2</v>
       </c>
-      <c r="J35" s="6" t="n">
+      <c r="K35" s="9" t="n">
         <v>99.7</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>2</v>
       </c>
-      <c r="L35" s="6" t="n">
+      <c r="M35" s="9" t="n">
         <v>24.2</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>4</v>
       </c>
-      <c r="N35" s="6" t="n">
+      <c r="O35" s="9" t="n">
         <v>16.3</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
         <v>1</v>
       </c>
-      <c r="P35" s="6" t="n">
+      <c r="Q35" s="9" t="n">
         <v>-37.8</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>13</v>
       </c>
-      <c r="R35" s="6" t="n">
+      <c r="S35" s="9" t="n">
         <v>6.8</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>6</v>
       </c>
-      <c r="T35" s="6" t="n">
+      <c r="U35" s="9" t="n">
         <v>20.7</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>8</v>
       </c>
     </row>
@@ -6660,56 +6838,61 @@
           <t>신에너지차</t>
         </is>
       </c>
-      <c r="D36" s="6" t="n">
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>0.7퍼센트 소폭 하락. 3개월 19.2퍼센트 약세로 전기차 과잉경쟁 부담 지속</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="F36" s="9" t="n">
         <v>-3.9</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="G36" s="9" t="n">
         <v>4.5</v>
       </c>
-      <c r="G36" s="6" t="n">
+      <c r="H36" s="9" t="n">
         <v>-19.2</v>
       </c>
-      <c r="H36" s="6" t="n">
+      <c r="I36" s="9" t="n">
         <v>-12.7</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>9</v>
       </c>
-      <c r="J36" s="6" t="n">
+      <c r="K36" s="9" t="n">
         <v>56.6</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>3</v>
       </c>
-      <c r="L36" s="6" t="n">
+      <c r="M36" s="9" t="n">
         <v>0.3</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>8</v>
       </c>
-      <c r="N36" s="6" t="n">
+      <c r="O36" s="9" t="n">
         <v>-29</v>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>12</v>
       </c>
-      <c r="P36" s="6" t="n">
+      <c r="Q36" s="9" t="n">
         <v>-28.9</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>10</v>
       </c>
-      <c r="R36" s="6" t="n">
+      <c r="S36" s="9" t="n">
         <v>41.9</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>2</v>
       </c>
-      <c r="T36" s="6" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
+      <c r="U36" s="9" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6727,58 +6910,63 @@
           <t>방산(军工)</t>
         </is>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>1.5퍼센트 하락. 3개월 19.1퍼센트 밀리며 성장 테마 전반의 조정에 동참</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n">
         <v>-1.5</v>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="F37" s="9" t="n">
         <v>-7</v>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="G37" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="H37" s="9" t="n">
         <v>-19.1</v>
       </c>
-      <c r="H37" s="6" t="n">
+      <c r="I37" s="9" t="n">
         <v>-20.6</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>11</v>
       </c>
-      <c r="J37" s="6" t="n">
+      <c r="K37" s="9" t="n">
         <v>31.8</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>6</v>
       </c>
-      <c r="L37" s="6" t="n">
+      <c r="M37" s="9" t="n">
         <v>8.5</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>6</v>
       </c>
-      <c r="N37" s="6" t="n">
+      <c r="O37" s="9" t="n">
         <v>-10.8</v>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>6</v>
       </c>
-      <c r="P37" s="6" t="n">
+      <c r="Q37" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="R37" t="n">
         <v>8</v>
       </c>
-      <c r="R37" s="6" t="n">
+      <c r="S37" s="9" t="n">
         <v>13.1</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>5</v>
       </c>
-      <c r="T37" s="6" t="n">
+      <c r="U37" s="9" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="U37" t="n">
+      <c r="V37" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6798,56 +6986,61 @@
           <t>태양광</t>
         </is>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>1.2퍼센트 하락. 3개월 24.4퍼센트로 낙폭 최대, 공급과잉 해소가 아직 확인되지 않음</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="F38" s="9" t="n">
         <v>-5</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="G38" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="G38" s="6" t="n">
+      <c r="H38" s="9" t="n">
         <v>-24.4</v>
       </c>
-      <c r="H38" s="6" t="n">
+      <c r="I38" s="9" t="n">
         <v>-12.5</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>8</v>
       </c>
-      <c r="J38" s="6" t="n">
+      <c r="K38" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>7</v>
       </c>
-      <c r="L38" s="6" t="n">
+      <c r="M38" s="9" t="n">
         <v>-14.9</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>13</v>
       </c>
-      <c r="N38" s="6" t="n">
+      <c r="O38" s="9" t="n">
         <v>-35.2</v>
       </c>
-      <c r="O38" t="n">
+      <c r="P38" t="n">
         <v>13</v>
       </c>
-      <c r="P38" s="6" t="n">
+      <c r="Q38" s="9" t="n">
         <v>-19.7</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="R38" t="n">
         <v>5</v>
       </c>
-      <c r="R38" s="6" t="n">
+      <c r="S38" s="9" t="n">
         <v>50.7</v>
       </c>
-      <c r="S38" t="n">
+      <c r="T38" t="n">
         <v>1</v>
       </c>
-      <c r="T38" s="6" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
+      <c r="U38" s="9" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6865,58 +7058,63 @@
           <t>백주(주류)</t>
         </is>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>0.5퍼센트 강보합. 내수 소비 부진에 YTD 마이너스 21.5퍼센트로 최하위권 유지</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="F39" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="F39" s="6" t="n">
+      <c r="G39" s="9" t="n">
         <v>1.2</v>
       </c>
-      <c r="G39" s="6" t="n">
+      <c r="H39" s="9" t="n">
         <v>-5.2</v>
       </c>
-      <c r="H39" s="6" t="n">
+      <c r="I39" s="9" t="n">
         <v>-21.5</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>13</v>
       </c>
-      <c r="J39" s="6" t="n">
+      <c r="K39" s="9" t="n">
         <v>-13</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>13</v>
       </c>
-      <c r="L39" s="6" t="n">
+      <c r="M39" s="9" t="n">
         <v>-11</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>11</v>
       </c>
-      <c r="N39" s="6" t="n">
+      <c r="O39" s="9" t="n">
         <v>-18.6</v>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>10</v>
       </c>
-      <c r="P39" s="6" t="n">
+      <c r="Q39" s="9" t="n">
         <v>-11.9</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="R39" t="n">
         <v>3</v>
       </c>
-      <c r="R39" s="6" t="n">
+      <c r="S39" s="9" t="n">
         <v>-3</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>9</v>
       </c>
-      <c r="T39" s="6" t="n">
+      <c r="U39" s="9" t="n">
         <v>336.4</v>
       </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6936,58 +7134,63 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D40" s="6" t="n">
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>1.5퍼센트 상승으로 A주 최강. 선행 6.5배 저평가와 배당이 기술주 회피 자금을 흡수</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="F40" s="9" t="n">
         <v>3.9</v>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="G40" s="9" t="n">
         <v>2.9</v>
       </c>
-      <c r="G40" s="6" t="n">
+      <c r="H40" s="9" t="n">
         <v>7.3</v>
       </c>
-      <c r="H40" s="6" t="n">
+      <c r="I40" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>5</v>
       </c>
-      <c r="J40" s="6" t="n">
+      <c r="K40" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>8</v>
       </c>
-      <c r="L40" s="6" t="n">
+      <c r="M40" s="9" t="n">
         <v>42.6</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>1</v>
       </c>
-      <c r="N40" s="6" t="n">
+      <c r="O40" s="9" t="n">
         <v>-3.3</v>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>5</v>
       </c>
-      <c r="P40" s="6" t="n">
+      <c r="Q40" s="9" t="n">
         <v>-4.8</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="R40" t="n">
         <v>1</v>
       </c>
-      <c r="R40" s="6" t="n">
+      <c r="S40" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
         <v>7</v>
       </c>
-      <c r="T40" s="6" t="n">
+      <c r="U40" s="9" t="n">
         <v>0.9</v>
       </c>
-      <c r="U40" t="n">
+      <c r="V40" t="n">
         <v>10</v>
       </c>
     </row>
@@ -7007,58 +7210,63 @@
           <t>유색금속</t>
         </is>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>0.2퍼센트 상승, 1개월 12.3퍼센트로 최강. 금값 사상최고에 금광 신고가 다수</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="F41" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="G41" s="9" t="n">
         <v>12.3</v>
       </c>
-      <c r="G41" s="6" t="n">
+      <c r="H41" s="9" t="n">
         <v>-7</v>
       </c>
-      <c r="H41" s="6" t="n">
+      <c r="I41" s="9" t="n">
         <v>1.1</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>4</v>
       </c>
-      <c r="J41" s="6" t="n">
+      <c r="K41" s="9" t="n">
         <v>101.1</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>1</v>
       </c>
-      <c r="L41" s="6" t="n">
+      <c r="M41" s="9" t="n">
         <v>4.1</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>7</v>
       </c>
-      <c r="N41" s="6" t="n">
+      <c r="O41" s="9" t="n">
         <v>-11.4</v>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>7</v>
       </c>
-      <c r="P41" s="6" t="n">
+      <c r="Q41" s="9" t="n">
         <v>-21.6</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="R41" t="n">
         <v>6</v>
       </c>
-      <c r="R41" s="6" t="n">
+      <c r="S41" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>3</v>
       </c>
-      <c r="T41" s="6" t="n">
+      <c r="U41" s="9" t="n">
         <v>43.2</v>
       </c>
-      <c r="U41" t="n">
+      <c r="V41" t="n">
         <v>7</v>
       </c>
     </row>
@@ -7078,58 +7286,63 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D42" s="6" t="n">
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>1.7퍼센트 하락. 1개월로는 5.8퍼센트 올랐으나 당일은 되돌림</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="n">
         <v>-1.7</v>
       </c>
-      <c r="E42" s="6" t="n">
+      <c r="F42" s="9" t="n">
         <v>-3.6</v>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="G42" s="9" t="n">
         <v>5.8</v>
       </c>
-      <c r="G42" s="6" t="n">
+      <c r="H42" s="9" t="n">
         <v>-13.2</v>
       </c>
-      <c r="H42" s="6" t="n">
+      <c r="I42" s="9" t="n">
         <v>-20.7</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>12</v>
       </c>
-      <c r="J42" s="6" t="n">
+      <c r="K42" s="9" t="n">
         <v>2.5</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>11</v>
       </c>
-      <c r="L42" s="6" t="n">
+      <c r="M42" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>9</v>
       </c>
-      <c r="N42" s="6" t="n">
+      <c r="O42" s="9" t="n">
         <v>-27</v>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>11</v>
       </c>
-      <c r="P42" s="6" t="n">
+      <c r="Q42" s="9" t="n">
         <v>-10.4</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="R42" t="n">
         <v>2</v>
       </c>
-      <c r="R42" s="6" t="n">
+      <c r="S42" s="9" t="n">
         <v>-6.4</v>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
         <v>11</v>
       </c>
-      <c r="T42" s="6" t="n">
+      <c r="U42" s="9" t="n">
         <v>-4.3</v>
       </c>
-      <c r="U42" t="n">
+      <c r="V42" t="n">
         <v>11</v>
       </c>
     </row>
@@ -7149,58 +7362,63 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="D43" s="6" t="n">
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>0.4퍼센트 강보합. 거래대금 회복 기대와 지수 약세가 상쇄</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="E43" s="6" t="n">
+      <c r="F43" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="G43" s="9" t="n">
         <v>-2.9</v>
       </c>
-      <c r="G43" s="6" t="n">
+      <c r="H43" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H43" s="6" t="n">
+      <c r="I43" s="9" t="n">
         <v>-11.9</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>7</v>
       </c>
-      <c r="J43" s="6" t="n">
+      <c r="K43" s="9" t="n">
         <v>3.5</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>10</v>
       </c>
-      <c r="L43" s="6" t="n">
+      <c r="M43" s="9" t="n">
         <v>29.7</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>2</v>
       </c>
-      <c r="N43" s="6" t="n">
+      <c r="O43" s="9" t="n">
         <v>3.8</v>
       </c>
-      <c r="O43" t="n">
+      <c r="P43" t="n">
         <v>2</v>
       </c>
-      <c r="P43" s="6" t="n">
+      <c r="Q43" s="9" t="n">
         <v>-26.1</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="R43" t="n">
         <v>8</v>
       </c>
-      <c r="R43" s="6" t="n">
+      <c r="S43" s="9" t="n">
         <v>-3.8</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>10</v>
       </c>
-      <c r="T43" s="6" t="n">
+      <c r="U43" s="9" t="n">
         <v>17.5</v>
       </c>
-      <c r="U43" t="n">
+      <c r="V43" t="n">
         <v>9</v>
       </c>
     </row>
@@ -7220,58 +7438,63 @@
           <t>의약</t>
         </is>
       </c>
-      <c r="D44" s="6" t="n">
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>3.1퍼센트 하락. 3개월 10.6퍼센트 상승분에 대한 차익실현 추정</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="n">
         <v>-3.1</v>
       </c>
-      <c r="E44" s="6" t="n">
+      <c r="F44" s="9" t="n">
         <v>-6.2</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="G44" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="G44" s="6" t="n">
+      <c r="H44" s="9" t="n">
         <v>10.6</v>
       </c>
-      <c r="H44" s="6" t="n">
+      <c r="I44" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="I44" t="n">
+      <c r="J44" t="n">
         <v>6</v>
       </c>
-      <c r="J44" s="6" t="n">
+      <c r="K44" s="9" t="n">
         <v>4.7</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>9</v>
       </c>
-      <c r="L44" s="6" t="n">
+      <c r="M44" s="9" t="n">
         <v>-12.2</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>12</v>
       </c>
-      <c r="N44" s="6" t="n">
+      <c r="O44" s="9" t="n">
         <v>-14</v>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>8</v>
       </c>
-      <c r="P44" s="6" t="n">
+      <c r="Q44" s="9" t="n">
         <v>-24.5</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>7</v>
       </c>
-      <c r="R44" s="6" t="n">
+      <c r="S44" s="9" t="n">
         <v>-15.7</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>13</v>
       </c>
-      <c r="T44" s="6" t="n">
+      <c r="U44" s="9" t="n">
         <v>62.9</v>
       </c>
-      <c r="U44" t="n">
+      <c r="V44" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7291,58 +7514,63 @@
           <t>소비(消费)</t>
         </is>
       </c>
-      <c r="D45" s="6" t="n">
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>0.2퍼센트 보합. 소비 회복 신호가 약해 방향성 부재</t>
+        </is>
+      </c>
+      <c r="E45" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="F45" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="G45" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="G45" s="6" t="n">
+      <c r="H45" s="9" t="n">
         <v>-2.9</v>
       </c>
-      <c r="H45" s="6" t="n">
+      <c r="I45" s="9" t="n">
         <v>-16.8</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>10</v>
       </c>
-      <c r="J45" s="6" t="n">
+      <c r="K45" s="9" t="n">
         <v>-2.9</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>12</v>
       </c>
-      <c r="L45" s="6" t="n">
+      <c r="M45" s="9" t="n">
         <v>-4.2</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>10</v>
       </c>
-      <c r="N45" s="6" t="n">
+      <c r="O45" s="9" t="n">
         <v>-18.3</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>9</v>
       </c>
-      <c r="P45" s="6" t="n">
+      <c r="Q45" s="9" t="n">
         <v>-13.4</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="R45" t="n">
         <v>4</v>
       </c>
-      <c r="R45" s="6" t="n">
+      <c r="S45" s="9" t="n">
         <v>-7.5</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>12</v>
       </c>
-      <c r="T45" s="6" t="n">
+      <c r="U45" s="9" t="n">
         <v>77.40000000000001</v>
       </c>
-      <c r="U45" t="n">
+      <c r="V45" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7354,7 +7582,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D45">
+  <conditionalFormatting sqref="E2:E45">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-4.5"/>
@@ -7366,7 +7594,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E45">
+  <conditionalFormatting sqref="F2:F45">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="-10.8"/>
@@ -7378,7 +7606,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F45">
+  <conditionalFormatting sqref="G2:G45">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="-9.300000000000001"/>
@@ -7390,7 +7618,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G45">
+  <conditionalFormatting sqref="H2:H45">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="-24.4"/>
@@ -7402,7 +7630,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H45">
+  <conditionalFormatting sqref="I2:I45">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="-21.5"/>
@@ -7414,7 +7642,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J45">
+  <conditionalFormatting sqref="K2:K45">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="-13"/>
@@ -7426,7 +7654,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L45">
+  <conditionalFormatting sqref="M2:M45">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="-14.9"/>
@@ -7438,7 +7666,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N45">
+  <conditionalFormatting sqref="O2:O45">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="num" val="-35.2"/>
@@ -7450,7 +7678,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P45">
+  <conditionalFormatting sqref="Q2:Q45">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="num" val="-37.8"/>
@@ -7462,7 +7690,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R45">
+  <conditionalFormatting sqref="S2:S45">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="-32.9"/>
@@ -7474,7 +7702,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T45">
+  <conditionalFormatting sqref="U2:U45">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="num" val="-32.7"/>
@@ -7588,12 +7816,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7641,15 +7869,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N2" s="8" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>비자(카드 결제망): 분기 매출 14% 증가 여진에 피퍼샌들러 목표가 430달러 상향, 3% 급등 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7693,15 +7925,19 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>마스터카드(카드 결제망): 트럼프 투자계좌 6월 매수 공시 부각, 결제 2강 동반 3%대 급등</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7749,15 +7985,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="8" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7805,10 +8041,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="8" t="inlineStr"/>
+      <c r="N5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7857,10 +8093,14 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" s="8" t="inlineStr"/>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>텍사스인스트루먼트(아날로그 반도체 대표주): 차량·산업 수요와 밸류 부담 우려로 아날로그 전반 약세</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7909,10 +8149,10 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" s="8" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -7961,10 +8201,10 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="8" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8017,15 +8257,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N9" s="8" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8069,10 +8309,10 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" s="8" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8125,14 +8365,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N11" s="8" t="inlineStr">
-        <is>
-          <t>(전일) (페루·멕시코 구리광산) 구리 강세 랠리와 2분기 실적 서프라이즈에 신고가</t>
+      <c r="N11" s="10" t="inlineStr">
+        <is>
+          <t>서던코퍼(구리 채굴·제련): 구리·금 강세로 신고가권 유지, 당일은 차익실현</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8181,15 +8421,15 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" s="8" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8233,10 +8473,14 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="8" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr">
+        <is>
+          <t>넥스트에라(최대 규제 전력·신재생 사업자): 30년 국채 5.27% 등 장기금리 상승에 배당주 할인율 부담</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8283,15 +8527,15 @@
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" s="8" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8335,15 +8579,15 @@
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" s="8" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8385,10 +8629,10 @@
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" s="8" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8437,15 +8681,15 @@
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" s="8" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8493,10 +8737,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N18" s="8" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8545,10 +8789,10 @@
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" s="8" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8601,14 +8845,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N20" s="8" t="inlineStr">
-        <is>
-          <t>(전일) (글로벌 구리광산 대형주) 구리 재고 타이트·AI 전력수요 기대에 신고가</t>
+      <c r="N20" s="10" t="inlineStr">
+        <is>
+          <t>프리포트맥모란(구리 채굴): 구리 강세 지속, 실물자산 선호 흐름</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8657,14 +8901,14 @@
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" s="8" t="inlineStr">
+      <c r="N21" s="10" t="inlineStr">
         <is>
           <t>(전일) 아그니코이글마인스(금 채굴): 달러 약세와 장기금리 반락으로 금값 급등 수혜</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8713,15 +8957,15 @@
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" s="8" t="inlineStr"/>
+      <c r="N22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8765,10 +9009,10 @@
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" s="8" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8817,10 +9061,10 @@
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" s="8" t="inlineStr"/>
+      <c r="N24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8873,15 +9117,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N25" s="8" t="inlineStr"/>
+      <c r="N25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8929,10 +9173,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N26" s="8" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -8981,10 +9225,10 @@
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" s="8" t="inlineStr"/>
+      <c r="N27" s="10" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9033,15 +9277,15 @@
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" s="8" t="inlineStr"/>
+      <c r="N28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9085,10 +9329,10 @@
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" s="8" t="inlineStr"/>
+      <c r="N29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9135,10 +9379,10 @@
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" s="8" t="inlineStr"/>
+      <c r="N30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9187,15 +9431,15 @@
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" s="8" t="inlineStr"/>
+      <c r="N31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9239,10 +9483,10 @@
         </is>
       </c>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" s="8" t="inlineStr"/>
+      <c r="N32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9291,15 +9535,19 @@
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" s="8" t="inlineStr"/>
+      <c r="N33" s="10" t="inlineStr">
+        <is>
+          <t>배릭마이닝(금 채굴): 국제 금값 사상최고 경신에 금광주 일제 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9343,10 +9591,10 @@
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" s="8" t="inlineStr"/>
+      <c r="N34" s="10" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9399,10 +9647,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N35" s="8" t="inlineStr"/>
+      <c r="N35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9451,15 +9699,15 @@
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" s="8" t="inlineStr"/>
+      <c r="N36" s="10" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9499,15 +9747,15 @@
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" s="8" t="inlineStr"/>
+      <c r="N37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9551,15 +9799,15 @@
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" s="8" t="inlineStr"/>
+      <c r="N38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9603,15 +9851,15 @@
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" s="8" t="inlineStr"/>
+      <c r="N39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9655,15 +9903,15 @@
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" s="8" t="inlineStr"/>
+      <c r="N40" s="10" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9707,10 +9955,10 @@
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" s="8" t="inlineStr"/>
+      <c r="N41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9759,19 +10007,19 @@
         </is>
       </c>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" s="8" t="inlineStr">
+      <c r="N42" s="10" t="inlineStr">
         <is>
           <t>(전일) (전력 규제 유틸리티) 국채금리 상승 압력에 유틸리티 섹터 전반 신저가</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9815,15 +10063,15 @@
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" s="8" t="inlineStr"/>
+      <c r="N43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9867,10 +10115,14 @@
         </is>
       </c>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" s="8" t="inlineStr"/>
+      <c r="N44" s="10" t="inlineStr">
+        <is>
+          <t>NXP반도체(차량용 반도체): 차량 수요 둔화 우려에 아날로그 동반 하락</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9919,10 +10171,10 @@
         </is>
       </c>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" s="8" t="inlineStr"/>
+      <c r="N45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9975,14 +10227,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N46" s="8" t="inlineStr">
+      <c r="N46" s="10" t="inlineStr">
         <is>
           <t>(전일) 벡톤디킨슨(주사기·진단 등 의료기기): 개별 뉴스 없음, 헬스케어 랠리 동반 상승</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10031,15 +10283,15 @@
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" s="8" t="inlineStr"/>
+      <c r="N47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10087,15 +10339,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N48" s="8" t="inlineStr"/>
+      <c r="N48" s="10" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10139,15 +10391,15 @@
         </is>
       </c>
       <c r="M49" t="inlineStr"/>
-      <c r="N49" s="8" t="inlineStr"/>
+      <c r="N49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10189,15 +10441,15 @@
         </is>
       </c>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" s="8" t="inlineStr"/>
+      <c r="N50" s="10" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10241,15 +10493,19 @@
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" s="8" t="inlineStr"/>
+      <c r="N51" s="10" t="inlineStr">
+        <is>
+          <t>비스트라(도매 발전사, AI 전력 대표주): 데이터센터 접속 심사 지연 우려로 고점 대비 되감김 지속</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="A52" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10293,10 +10549,10 @@
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" s="8" t="inlineStr"/>
+      <c r="N52" s="10" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10349,15 +10605,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N53" s="8" t="inlineStr"/>
+      <c r="N53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="A54" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10401,10 +10657,10 @@
         </is>
       </c>
       <c r="M54" t="inlineStr"/>
-      <c r="N54" s="8" t="inlineStr"/>
+      <c r="N54" s="10" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10453,15 +10709,15 @@
         </is>
       </c>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" s="8" t="inlineStr"/>
+      <c r="N55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B56" s="7" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10509,10 +10765,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N56" s="8" t="inlineStr"/>
+      <c r="N56" s="10" t="inlineStr">
+        <is>
+          <t>익스피디아(온라인 여행예약 플랫폼): 개별 뉴스 없음, 소비 관련주로 자금이동 추정</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10561,14 +10821,14 @@
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
-      <c r="N57" s="8" t="inlineStr">
+      <c r="N57" s="10" t="inlineStr">
         <is>
           <t>(전일) (금 채굴) 금값 2개월래 최고 4530달러 부근, 금광주 동반 신고가</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10617,14 +10877,14 @@
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" s="8" t="inlineStr">
+      <c r="N58" s="10" t="inlineStr">
         <is>
           <t>(전일) (프레스티지 화장품) 분기 EPS 서프라이즈와 중국 매출 회복에 목표가 줄상향</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10673,10 +10933,10 @@
         </is>
       </c>
       <c r="M59" t="inlineStr"/>
-      <c r="N59" s="8" t="inlineStr"/>
+      <c r="N59" s="10" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="inlineStr">
+      <c r="A60" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -10729,14 +10989,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N60" s="8" t="inlineStr">
+      <c r="N60" s="10" t="inlineStr">
         <is>
           <t>(전일) (전력·가스 규제 유틸리티) 국채수익률 고점권 유지에 금리민감주 매도</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10785,10 +11045,10 @@
         </is>
       </c>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" s="8" t="inlineStr"/>
+      <c r="N61" s="10" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="inlineStr">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10841,10 +11101,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N62" s="8" t="inlineStr"/>
+      <c r="N62" s="10" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="inlineStr">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10897,19 +11157,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N63" s="8" t="inlineStr">
+      <c r="N63" s="10" t="inlineStr">
         <is>
           <t>(전일) (유전체 시퀀싱 장비) 2분기 매출 서프라이즈 여진에 신고가 지속</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr">
+      <c r="A64" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10953,15 +11213,15 @@
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" s="8" t="inlineStr"/>
+      <c r="N64" s="10" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="inlineStr">
+      <c r="A65" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11005,10 +11265,10 @@
         </is>
       </c>
       <c r="M65" t="inlineStr"/>
-      <c r="N65" s="8" t="inlineStr"/>
+      <c r="N65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="inlineStr">
+      <c r="A66" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11057,10 +11317,10 @@
         </is>
       </c>
       <c r="M66" t="inlineStr"/>
-      <c r="N66" s="8" t="inlineStr"/>
+      <c r="N66" s="10" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="inlineStr">
+      <c r="A67" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11109,15 +11369,15 @@
         </is>
       </c>
       <c r="M67" t="inlineStr"/>
-      <c r="N67" s="8" t="inlineStr"/>
+      <c r="N67" s="10" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B68" s="7" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11165,15 +11425,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N68" s="8" t="inlineStr"/>
+      <c r="N68" s="10" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="inlineStr">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B69" s="7" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11221,10 +11481,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N69" s="8" t="inlineStr"/>
+      <c r="N69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="inlineStr">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11273,10 +11533,10 @@
         </is>
       </c>
       <c r="M70" t="inlineStr"/>
-      <c r="N70" s="8" t="inlineStr"/>
+      <c r="N70" s="10" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="inlineStr">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11325,15 +11585,15 @@
         </is>
       </c>
       <c r="M71" t="inlineStr"/>
-      <c r="N71" s="8" t="inlineStr"/>
+      <c r="N71" s="10" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="inlineStr">
+      <c r="A72" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B72" s="7" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11377,15 +11637,15 @@
         </is>
       </c>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" s="8" t="inlineStr"/>
+      <c r="N72" s="10" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="inlineStr">
+      <c r="A73" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B73" s="7" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11429,10 +11689,14 @@
         </is>
       </c>
       <c r="M73" t="inlineStr"/>
-      <c r="N73" s="8" t="inlineStr"/>
+      <c r="N73" s="10" t="inlineStr">
+        <is>
+          <t>달러트리(초저가 잡화 체인): 개별 뉴스 없음, 저가 소매 동반 강세 추정</t>
+        </is>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="inlineStr">
+      <c r="A74" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11481,15 +11745,15 @@
         </is>
       </c>
       <c r="M74" t="inlineStr"/>
-      <c r="N74" s="8" t="inlineStr"/>
+      <c r="N74" s="10" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="inlineStr">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B75" s="7" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11533,15 +11797,15 @@
         </is>
       </c>
       <c r="M75" t="inlineStr"/>
-      <c r="N75" s="8" t="inlineStr"/>
+      <c r="N75" s="10" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="inlineStr">
+      <c r="A76" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B76" s="7" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11585,15 +11849,19 @@
         </is>
       </c>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" s="8" t="inlineStr"/>
+      <c r="N76" s="10" t="inlineStr">
+        <is>
+          <t>글로벌파운드리(자동차·산업용 성숙공정 파운드리): 아날로그·차량용 수요 부진 우려에 반도체 동반 급락</t>
+        </is>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="inlineStr">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B77" s="7" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11641,15 +11909,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N77" s="8" t="inlineStr"/>
+      <c r="N77" s="10" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="inlineStr">
+      <c r="A78" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B78" s="7" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11697,15 +11965,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N78" s="8" t="inlineStr"/>
+      <c r="N78" s="10" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="inlineStr">
+      <c r="A79" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B79" s="7" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11749,15 +12017,19 @@
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
-      <c r="N79" s="8" t="inlineStr"/>
+      <c r="N79" s="10" t="inlineStr">
+        <is>
+          <t>JB헌트(화물운송·인터모달 물류): 화물 수요 부진 지속, 개별 촉매 없이 신저가</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="inlineStr">
+      <c r="A80" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B80" s="7" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11805,10 +12077,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N80" s="8" t="inlineStr"/>
+      <c r="N80" s="10" t="inlineStr">
+        <is>
+          <t>NRG에너지(텍사스 중심 도매 발전사): 텍사스 접속 중단 직격, 전력 수요 반영 시점 후퇴</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="inlineStr">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11857,10 +12133,10 @@
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
-      <c r="N81" s="8" t="inlineStr"/>
+      <c r="N81" s="10" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="inlineStr">
+      <c r="A82" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -11909,19 +12185,19 @@
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
-      <c r="N82" s="8" t="inlineStr">
+      <c r="N82" s="10" t="inlineStr">
         <is>
           <t>(전일) 커티스라이트(방산·원자력 부품): 특별한 뉴스 없음(8월 실적 이후 밸류에이션 조정 지속)</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="inlineStr">
+      <c r="A83" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B83" s="7" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11965,10 +12241,10 @@
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
-      <c r="N83" s="8" t="inlineStr"/>
+      <c r="N83" s="10" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="4" t="inlineStr">
+      <c r="A84" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12021,10 +12297,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N84" s="8" t="inlineStr"/>
+      <c r="N84" s="10" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="4" t="inlineStr">
+      <c r="A85" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12073,10 +12349,10 @@
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
-      <c r="N85" s="8" t="inlineStr"/>
+      <c r="N85" s="10" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="4" t="inlineStr">
+      <c r="A86" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12123,15 +12399,15 @@
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
-      <c r="N86" s="8" t="inlineStr"/>
+      <c r="N86" s="10" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="inlineStr">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B87" s="7" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12173,10 +12449,10 @@
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
-      <c r="N87" s="8" t="inlineStr"/>
+      <c r="N87" s="10" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="5" t="inlineStr">
+      <c r="A88" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12229,10 +12505,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N88" s="8" t="inlineStr"/>
+      <c r="N88" s="10" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="4" t="inlineStr">
+      <c r="A89" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12281,10 +12557,10 @@
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
-      <c r="N89" s="8" t="inlineStr"/>
+      <c r="N89" s="10" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="4" t="inlineStr">
+      <c r="A90" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12333,15 +12609,15 @@
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
-      <c r="N90" s="8" t="inlineStr"/>
+      <c r="N90" s="10" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="5" t="inlineStr">
+      <c r="A91" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B91" s="7" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12385,15 +12661,15 @@
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
-      <c r="N91" s="8" t="inlineStr"/>
+      <c r="N91" s="10" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="5" t="inlineStr">
+      <c r="A92" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B92" s="7" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12437,15 +12713,15 @@
         </is>
       </c>
       <c r="M92" t="inlineStr"/>
-      <c r="N92" s="8" t="inlineStr"/>
+      <c r="N92" s="10" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="inlineStr">
+      <c r="A93" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B93" s="7" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12489,10 +12765,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N93" s="8" t="inlineStr"/>
+      <c r="N93" s="10" t="inlineStr">
+        <is>
+          <t>페덱스프레이트(페덱스에서 분할한 소량화물 운송): 화물 업황 약세로 JB헌트와 동반 신저가</t>
+        </is>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" s="5" t="inlineStr">
+      <c r="A94" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -12541,10 +12821,10 @@
         </is>
       </c>
       <c r="M94" t="inlineStr"/>
-      <c r="N94" s="8" t="inlineStr"/>
+      <c r="N94" s="10" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="4" t="inlineStr">
+      <c r="A95" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12593,10 +12873,10 @@
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
-      <c r="N95" s="8" t="inlineStr"/>
+      <c r="N95" s="10" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="4" t="inlineStr">
+      <c r="A96" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12645,15 +12925,15 @@
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
-      <c r="N96" s="8" t="inlineStr"/>
+      <c r="N96" s="10" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="A97" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B97" s="7" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12697,15 +12977,15 @@
         </is>
       </c>
       <c r="M97" t="inlineStr"/>
-      <c r="N97" s="8" t="inlineStr"/>
+      <c r="N97" s="10" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="5" t="inlineStr">
+      <c r="A98" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B98" s="7" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12749,15 +13029,15 @@
         </is>
       </c>
       <c r="M98" t="inlineStr"/>
-      <c r="N98" s="8" t="inlineStr"/>
+      <c r="N98" s="10" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="4" t="inlineStr">
+      <c r="A99" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B99" s="7" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12799,15 +13079,15 @@
         </is>
       </c>
       <c r="M99" t="inlineStr"/>
-      <c r="N99" s="8" t="inlineStr"/>
+      <c r="N99" s="10" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="4" t="inlineStr">
+      <c r="A100" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B100" s="7" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12851,15 +13131,15 @@
         </is>
       </c>
       <c r="M100" t="inlineStr"/>
-      <c r="N100" s="8" t="inlineStr"/>
+      <c r="N100" s="10" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="4" t="inlineStr">
+      <c r="A101" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B101" s="7" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12907,15 +13187,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N101" s="8" t="inlineStr"/>
+      <c r="N101" s="10" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="4" t="inlineStr">
+      <c r="A102" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B102" s="7" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12959,10 +13239,10 @@
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
-      <c r="N102" s="8" t="inlineStr"/>
+      <c r="N102" s="10" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="4" t="inlineStr">
+      <c r="A103" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13015,15 +13295,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N103" s="8" t="inlineStr"/>
+      <c r="N103" s="10" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="5" t="inlineStr">
+      <c r="A104" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B104" s="7" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13067,15 +13347,15 @@
         </is>
       </c>
       <c r="M104" t="inlineStr"/>
-      <c r="N104" s="8" t="inlineStr"/>
+      <c r="N104" s="10" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="4" t="inlineStr">
+      <c r="A105" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B105" s="7" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13119,15 +13399,15 @@
         </is>
       </c>
       <c r="M105" t="inlineStr"/>
-      <c r="N105" s="8" t="inlineStr"/>
+      <c r="N105" s="10" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="5" t="inlineStr">
+      <c r="A106" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B106" s="7" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13175,10 +13455,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N106" s="8" t="inlineStr"/>
+      <c r="N106" s="10" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="4" t="inlineStr">
+      <c r="A107" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13227,10 +13507,10 @@
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
-      <c r="N107" s="8" t="inlineStr"/>
+      <c r="N107" s="10" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="5" t="inlineStr">
+      <c r="A108" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13279,15 +13559,15 @@
         </is>
       </c>
       <c r="M108" t="inlineStr"/>
-      <c r="N108" s="8" t="inlineStr"/>
+      <c r="N108" s="10" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="4" t="inlineStr">
+      <c r="A109" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B109" s="7" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13335,15 +13615,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N109" s="8" t="inlineStr"/>
+      <c r="N109" s="10" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="5" t="inlineStr">
+      <c r="A110" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B110" s="7" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13387,15 +13667,15 @@
         </is>
       </c>
       <c r="M110" t="inlineStr"/>
-      <c r="N110" s="8" t="inlineStr"/>
+      <c r="N110" s="10" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="5" t="inlineStr">
+      <c r="A111" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B111" s="7" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13439,10 +13719,10 @@
         </is>
       </c>
       <c r="M111" t="inlineStr"/>
-      <c r="N111" s="8" t="inlineStr"/>
+      <c r="N111" s="10" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="5" t="inlineStr">
+      <c r="A112" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13491,15 +13771,15 @@
         </is>
       </c>
       <c r="M112" t="inlineStr"/>
-      <c r="N112" s="8" t="inlineStr"/>
+      <c r="N112" s="10" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="5" t="inlineStr">
+      <c r="A113" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B113" s="7" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13541,15 +13821,19 @@
         </is>
       </c>
       <c r="M113" t="inlineStr"/>
-      <c r="N113" s="8" t="inlineStr"/>
+      <c r="N113" s="10" t="inlineStr">
+        <is>
+          <t>탈렌에너지(원전 보유 도매 발전사): 텍사스 데이터센터 접속 중단 감사로 전력 수요 인식 지연, 신저가</t>
+        </is>
+      </c>
     </row>
     <row r="114">
-      <c r="A114" s="4" t="inlineStr">
+      <c r="A114" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B114" s="7" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13593,10 +13877,10 @@
         </is>
       </c>
       <c r="M114" t="inlineStr"/>
-      <c r="N114" s="8" t="inlineStr"/>
+      <c r="N114" s="10" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="4" t="inlineStr">
+      <c r="A115" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13643,15 +13927,15 @@
         </is>
       </c>
       <c r="M115" t="inlineStr"/>
-      <c r="N115" s="8" t="inlineStr"/>
+      <c r="N115" s="10" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="4" t="inlineStr">
+      <c r="A116" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B116" s="7" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13695,10 +13979,10 @@
         </is>
       </c>
       <c r="M116" t="inlineStr"/>
-      <c r="N116" s="8" t="inlineStr"/>
+      <c r="N116" s="10" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="4" t="inlineStr">
+      <c r="A117" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13751,14 +14035,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N117" s="8" t="inlineStr">
-        <is>
-          <t>(전일) (저가 잡화 소매체인) 실적 발표를 앞둔 매수세와 목표가 상향</t>
+      <c r="N117" s="10" t="inlineStr">
+        <is>
+          <t>파이브빌로우(초저가 잡화 체인): 신규 촉매 미확인, 저가 소매 동반 강세 추정</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="5" t="inlineStr">
+      <c r="A118" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13807,10 +14091,10 @@
         </is>
       </c>
       <c r="M118" t="inlineStr"/>
-      <c r="N118" s="8" t="inlineStr"/>
+      <c r="N118" s="10" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="5" t="inlineStr">
+      <c r="A119" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -13863,15 +14147,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N119" s="8" t="inlineStr"/>
+      <c r="N119" s="10" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="5" t="inlineStr">
+      <c r="A120" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B120" s="7" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13919,10 +14203,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N120" s="8" t="inlineStr"/>
+      <c r="N120" s="10" t="inlineStr">
+        <is>
+          <t>BWX테크놀로지스(원자로 부품·소형모듈원전): 개별 악재 없음, AI 전력 테마 되감김에 동반 하락 추정</t>
+        </is>
+      </c>
     </row>
     <row r="121">
-      <c r="A121" s="4" t="inlineStr">
+      <c r="A121" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13975,10 +14263,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N121" s="8" t="inlineStr"/>
+      <c r="N121" s="10" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="4" t="inlineStr">
+      <c r="A122" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14031,15 +14319,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N122" s="8" t="inlineStr"/>
+      <c r="N122" s="10" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="4" t="inlineStr">
+      <c r="A123" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B123" s="7" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14083,10 +14371,10 @@
         </is>
       </c>
       <c r="M123" t="inlineStr"/>
-      <c r="N123" s="8" t="inlineStr"/>
+      <c r="N123" s="10" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="5" t="inlineStr">
+      <c r="A124" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14135,14 +14423,14 @@
         </is>
       </c>
       <c r="M124" t="inlineStr"/>
-      <c r="N124" s="8" t="inlineStr">
+      <c r="N124" s="10" t="inlineStr">
         <is>
           <t>(전일) (태양광 트래커·에너지저장) 실적 부진과 목표주가 하향 여진 추정</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="4" t="inlineStr">
+      <c r="A125" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14189,10 +14477,10 @@
         </is>
       </c>
       <c r="M125" t="inlineStr"/>
-      <c r="N125" s="8" t="inlineStr"/>
+      <c r="N125" s="10" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="5" t="inlineStr">
+      <c r="A126" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14241,10 +14529,10 @@
         </is>
       </c>
       <c r="M126" t="inlineStr"/>
-      <c r="N126" s="8" t="inlineStr"/>
+      <c r="N126" s="10" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="5" t="inlineStr">
+      <c r="A127" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14297,14 +14585,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N127" s="8" t="inlineStr">
+      <c r="N127" s="10" t="inlineStr">
         <is>
           <t>(전일) 왓츠코(냉난방공조 유통): 30년물 금리 2007년래 최고에 주택·건자재 수요 우려 확산</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="5" t="inlineStr">
+      <c r="A128" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14355,19 +14643,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N128" s="8" t="inlineStr">
+      <c r="N128" s="10" t="inlineStr">
         <is>
           <t>(전일) (산업용 송풍·공조장비) 51억유로 규모 인수 자금조달 부담 우려로 신저가</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="4" t="inlineStr">
+      <c r="A129" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B129" s="7" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14409,10 +14697,10 @@
         </is>
       </c>
       <c r="M129" t="inlineStr"/>
-      <c r="N129" s="8" t="inlineStr"/>
+      <c r="N129" s="10" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="4" t="inlineStr">
+      <c r="A130" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14461,10 +14749,10 @@
         </is>
       </c>
       <c r="M130" t="inlineStr"/>
-      <c r="N130" s="8" t="inlineStr"/>
+      <c r="N130" s="10" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="4" t="inlineStr">
+      <c r="A131" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14513,10 +14801,10 @@
         </is>
       </c>
       <c r="M131" t="inlineStr"/>
-      <c r="N131" s="8" t="inlineStr"/>
+      <c r="N131" s="10" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="4" t="inlineStr">
+      <c r="A132" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14569,15 +14857,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N132" s="8" t="inlineStr"/>
+      <c r="N132" s="10" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="4" t="inlineStr">
+      <c r="A133" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B133" s="7" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14623,15 +14911,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N133" s="8" t="inlineStr"/>
+      <c r="N133" s="10" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="4" t="inlineStr">
+      <c r="A134" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B134" s="7" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14673,10 +14961,10 @@
         </is>
       </c>
       <c r="M134" t="inlineStr"/>
-      <c r="N134" s="8" t="inlineStr"/>
+      <c r="N134" s="10" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="4" t="inlineStr">
+      <c r="A135" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14725,19 +15013,19 @@
         </is>
       </c>
       <c r="M135" t="inlineStr"/>
-      <c r="N135" s="8" t="inlineStr">
+      <c r="N135" s="10" t="inlineStr">
         <is>
           <t>(전일) (캐나다계 금광 채굴) 금값 3개월래 최고치 랠리와 CIBC 투자의견 상향</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="4" t="inlineStr">
+      <c r="A136" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B136" s="7" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14785,10 +15073,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N136" s="8" t="inlineStr"/>
+      <c r="N136" s="10" t="inlineStr">
+        <is>
+          <t>인스타카트(온라인 식료품 배달): 개별 뉴스 없음, 광고매출 성장 기대 지속 추정</t>
+        </is>
+      </c>
     </row>
     <row r="137">
-      <c r="A137" s="5" t="inlineStr">
+      <c r="A137" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -14837,10 +15129,10 @@
         </is>
       </c>
       <c r="M137" t="inlineStr"/>
-      <c r="N137" s="8" t="inlineStr"/>
+      <c r="N137" s="10" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="4" t="inlineStr">
+      <c r="A138" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14889,15 +15181,15 @@
         </is>
       </c>
       <c r="M138" t="inlineStr"/>
-      <c r="N138" s="8" t="inlineStr"/>
+      <c r="N138" s="10" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="4" t="inlineStr">
+      <c r="A139" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B139" s="7" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14941,15 +15233,15 @@
         </is>
       </c>
       <c r="M139" t="inlineStr"/>
-      <c r="N139" s="8" t="inlineStr"/>
+      <c r="N139" s="10" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="5" t="inlineStr">
+      <c r="A140" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B140" s="7" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14993,10 +15285,10 @@
         </is>
       </c>
       <c r="M140" t="inlineStr"/>
-      <c r="N140" s="8" t="inlineStr"/>
+      <c r="N140" s="10" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="4" t="inlineStr">
+      <c r="A141" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15045,15 +15337,15 @@
         </is>
       </c>
       <c r="M141" t="inlineStr"/>
-      <c r="N141" s="8" t="inlineStr"/>
+      <c r="N141" s="10" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="5" t="inlineStr">
+      <c r="A142" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B142" s="7" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15093,10 +15385,14 @@
         </is>
       </c>
       <c r="M142" t="inlineStr"/>
-      <c r="N142" s="8" t="inlineStr"/>
+      <c r="N142" s="10" t="inlineStr">
+        <is>
+          <t>오로라이노베이션(자율주행 트럭 기술): 8월 초 실적부진·내부자 매도 예고 여진에 8.8% 급락</t>
+        </is>
+      </c>
     </row>
     <row r="143">
-      <c r="A143" s="5" t="inlineStr">
+      <c r="A143" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -15143,15 +15439,15 @@
         </is>
       </c>
       <c r="M143" t="inlineStr"/>
-      <c r="N143" s="8" t="inlineStr"/>
+      <c r="N143" s="10" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="4" t="inlineStr">
+      <c r="A144" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B144" s="7" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15195,10 +15491,10 @@
         </is>
       </c>
       <c r="M144" t="inlineStr"/>
-      <c r="N144" s="8" t="inlineStr"/>
+      <c r="N144" s="10" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="5" t="inlineStr">
+      <c r="A145" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -15245,19 +15541,19 @@
         </is>
       </c>
       <c r="M145" t="inlineStr"/>
-      <c r="N145" s="8" t="inlineStr">
+      <c r="N145" s="10" t="inlineStr">
         <is>
           <t>(전일) 인라이트리뉴어블(태양광·풍력 발전 개발): 특별한 뉴스 없음(밸류에이션 부담·차익실현 추정)</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="5" t="inlineStr">
+      <c r="A146" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B146" s="7" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15299,10 +15595,10 @@
         </is>
       </c>
       <c r="M146" t="inlineStr"/>
-      <c r="N146" s="8" t="inlineStr"/>
+      <c r="N146" s="10" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="5" t="inlineStr">
+      <c r="A147" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -15351,15 +15647,15 @@
         </is>
       </c>
       <c r="M147" t="inlineStr"/>
-      <c r="N147" s="8" t="inlineStr"/>
+      <c r="N147" s="10" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="4" t="inlineStr">
+      <c r="A148" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B148" s="7" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15407,15 +15703,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N148" s="8" t="inlineStr"/>
+      <c r="N148" s="10" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="4" t="inlineStr">
+      <c r="A149" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B149" s="7" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15459,10 +15755,10 @@
         </is>
       </c>
       <c r="M149" t="inlineStr"/>
-      <c r="N149" s="8" t="inlineStr"/>
+      <c r="N149" s="10" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="5" t="inlineStr">
+      <c r="A150" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -15511,15 +15807,15 @@
         </is>
       </c>
       <c r="M150" t="inlineStr"/>
-      <c r="N150" s="8" t="inlineStr"/>
+      <c r="N150" s="10" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="4" t="inlineStr">
+      <c r="A151" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B151" s="7" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15567,10 +15863,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N151" s="8" t="inlineStr"/>
+      <c r="N151" s="10" t="inlineStr">
+        <is>
+          <t>퍼스트캐시(전당포·소액대출 체인): 개별 뉴스 없음, 소비 하향이동 수혜 기대 지속 추정</t>
+        </is>
+      </c>
     </row>
     <row r="152">
-      <c r="A152" s="4" t="inlineStr">
+      <c r="A152" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15623,15 +15923,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N152" s="8" t="inlineStr"/>
+      <c r="N152" s="10" t="inlineStr">
+        <is>
+          <t>페이컴(급여·인사관리 소프트웨어): 신규 촉매 미확인, 소프트웨어 강세에 동반</t>
+        </is>
+      </c>
     </row>
     <row r="153">
-      <c r="A153" s="4" t="inlineStr">
+      <c r="A153" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B153" s="7" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15673,15 +15977,19 @@
         </is>
       </c>
       <c r="M153" t="inlineStr"/>
-      <c r="N153" s="8" t="inlineStr"/>
+      <c r="N153" s="10" t="inlineStr">
+        <is>
+          <t>딜라드(중가 백화점 체인): 개별 뉴스 없음, 주간 8%대 상승 연장</t>
+        </is>
+      </c>
     </row>
     <row r="154">
-      <c r="A154" s="4" t="inlineStr">
+      <c r="A154" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B154" s="7" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15725,7 +16033,7 @@
         </is>
       </c>
       <c r="M154" t="inlineStr"/>
-      <c r="N154" s="8" t="inlineStr"/>
+      <c r="N154" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N154"/>
@@ -15831,12 +16139,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -15880,10 +16188,14 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>이토추상사(종합상사): 3000억엔 자사주매입·사상최대 순이익 모멘텀 지속, 상사 섹터 강세</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15934,14 +16246,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N3" s="8" t="inlineStr">
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>(전일) (일본 통신 1위 NTT그룹) 방어주 선호 속 매수세로 신고가</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15992,14 +16304,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="8" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>(전일) (포털·핀테크 플랫폼) 페이페이 결제액 34.9% 성장 등 실적 호조 지속</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16048,14 +16360,14 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="8" t="inlineStr">
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>(전일) (비철금속 제련·금은동 광업) 금·구리 급등에 상장 이래 최고가 경신</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16108,14 +16420,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="8" t="inlineStr">
+      <c r="N6" s="10" t="inlineStr">
         <is>
           <t>(전일) (해운 3사, 컨테이너·벌크) 벌크운임 반등에 해운주 동반 신고가</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16168,10 +16480,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="8" t="inlineStr"/>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>상선미쓰이(해운 대형사): 신규 재료 없음, 중동 긴장에 따른 운임 상승 기대 지속</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16220,14 +16536,14 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="8" t="inlineStr">
+      <c r="N8" s="10" t="inlineStr">
         <is>
           <t>(전일) (증권·은행 겸영 금융지주) 금리 상승 수혜 기대에 신고가</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16280,19 +16596,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N9" s="8" t="inlineStr">
+      <c r="N9" s="10" t="inlineStr">
         <is>
           <t>(전일) (해운 3사, 컨테이너·벌크) 벌크운임 반등에 해운주 동반 신고가</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16338,7 +16654,11 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N10" s="8" t="inlineStr"/>
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t>젠쇼홀딩스(규동 스키야 등 외식 체인): 개별 뉴스 없음, 내수 소비주 수급 강세 추정</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N10"/>
@@ -16444,7 +16764,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16493,19 +16813,19 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr">
+      <c r="N2" s="10" t="inlineStr">
         <is>
           <t>(전일) (중국 최대 금·구리 광산업체) 금·구리 동반 강세에 광산주 급등</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16547,10 +16867,14 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>시노펙 H주(중국 최대 정유·화학): 상반기 순이익 19% 증가 실적 호조에 5.9% 급등</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16597,10 +16921,10 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" s="8" t="inlineStr"/>
+      <c r="N4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16647,14 +16971,14 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" s="8" t="inlineStr">
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>(전일) (쯔진광업의 금 사업 자회사) 금값 랠리에 모기업 후광 업고 급등</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -16707,14 +17031,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="8" t="inlineStr">
+      <c r="N6" s="10" t="inlineStr">
         <is>
           <t>(전일) (제약) 상반기 매출 1.9%·조정순이익 12.7% 감소로 업종과 반대로 급락</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16767,19 +17091,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="8" t="inlineStr">
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>(전일) 코스코해운홀딩스(컨테이너 해운): 특별한 뉴스 없음(호르무즈발 운임 강세 지속 추정)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16823,10 +17147,14 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="8" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>화훙반도체(중국 2위 파운드리): 알리바바 대규모 유상증자로 AI 투자 자금조달 우려 확산, 동반 급락</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16871,14 +17199,14 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" s="8" t="inlineStr">
+      <c r="N9" s="10" t="inlineStr">
         <is>
           <t>(전일) (홍콩 지하철 운영·역세권 개발) 특별한 뉴스 없음, 홍콩 강세장 속 고배당 수급 추정</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16929,14 +17257,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N10" s="8" t="inlineStr">
+      <c r="N10" s="10" t="inlineStr">
         <is>
           <t>(전일) (홍콩 최대 전력회사) 특별한 뉴스 없음, 홍콩 강세장 속 고배당 수급 추정</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16981,14 +17309,14 @@
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" s="8" t="inlineStr">
+      <c r="N11" s="10" t="inlineStr">
         <is>
           <t>(전일) (중국 대표 금광업체) 금값 4,600달러선 회복에 금광주 동반 급등</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -17031,10 +17359,10 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" s="8" t="inlineStr"/>
+      <c r="N12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -17079,19 +17407,19 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="8" t="inlineStr">
+      <c r="N13" s="10" t="inlineStr">
         <is>
           <t>(전일) (마카오 카지노·리조트) 여름 성수기 마카오 매출 회복 기대에 강세</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17135,15 +17463,19 @@
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" s="8" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr">
+        <is>
+          <t>베이커자오팡(주택 중개 플랫폼): 2분기 실적 컨센서스 상회, 골드만·씨티 목표가 상향</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17189,10 +17521,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N15" s="8" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr">
+        <is>
+          <t>콰이서우(숏폼 동영상 플랫폼): 8월 19일 실적 후 약세 지속, 내수 영업이익 급감·해외 적자전환</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -17237,10 +17573,10 @@
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" s="8" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -17289,15 +17625,15 @@
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" s="8" t="inlineStr"/>
+      <c r="N17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17337,15 +17673,19 @@
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" s="8" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr">
+        <is>
+          <t>파워어셋(홍콩 전력·에너지 자산 지주): 기술주 회피 자금의 배당 방어주 선호로 신고가권, 당일은 차익실현</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17389,10 +17729,10 @@
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" s="8" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -17443,15 +17783,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N20" s="8" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17491,10 +17831,14 @@
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" s="8" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr">
+        <is>
+          <t>톈수즈신(중국 AI 가속칩 설계): 알리바바 102억달러 유상증자發 AI 밸류체인 동반 급락, 10.6% 하락</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -17541,19 +17885,19 @@
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" s="8" t="inlineStr">
+      <c r="N22" s="10" t="inlineStr">
         <is>
           <t>(전일) (금광 채굴업체) 금값 3개월래 최고 랠리에 금광주 급등세 지속</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17599,10 +17943,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N23" s="8" t="inlineStr"/>
+      <c r="N23" s="10" t="inlineStr">
+        <is>
+          <t>상하이전기 H주(발전설비 제조): 개별 뉴스 없음, 전력설비 섹터 약세 동반 추정</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -17653,19 +18001,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N24" s="8" t="inlineStr">
+      <c r="N24" s="10" t="inlineStr">
         <is>
           <t>(전일) (금광 채굴) 금값 급등과 실적 호조 여진으로 52주 신고가</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17711,15 +18059,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N25" s="8" t="inlineStr"/>
+      <c r="N25" s="10" t="inlineStr">
+        <is>
+          <t>싸이리스그룹(화웨이 협력 전기차 제조): 상반기 순손실 전환 전망, 원자재비 상승·자산손상 반영</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17763,7 +18115,11 @@
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" s="8" t="inlineStr"/>
+      <c r="N26" s="10" t="inlineStr">
+        <is>
+          <t>자오진광업(금 채굴): 국제 금값 사상최고 경신에 금광주 동반 강세</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:N26"/>
@@ -17869,12 +18225,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17918,15 +18274,19 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr"/>
+      <c r="N2" s="10" t="inlineStr">
+        <is>
+          <t>캄브리콘(중국 대표 AI 가속칩 설계): 장기금리 상승에 고밸류 성장주 조정, AI칩 경쟁사 상장으로 희소성 약화</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17966,10 +18326,14 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr">
+        <is>
+          <t>시노펙 A주(중국 최대 정유·화학): 상반기 순이익 19.3% 증가와 자사주매입 계획에 4.5% 상승</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -18018,14 +18382,14 @@
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" s="8" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>(전일) (AI 반도체 설계) 특별한 호재 부재, 차익실현과 수급 이탈 추정</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -18074,14 +18438,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="8" t="inlineStr">
-        <is>
-          <t>(전일) 중신은행(전국구 주식제 상업은행): 테크주 급락 자금이 저평가 고배당 은행으로 이동</t>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>중신은행 A주(중국 상업은행): 기술주 급락 속 저평가·고배당 선호로 자금이동, 장중 사상최고가</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -18130,14 +18494,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N6" s="8" t="inlineStr">
-        <is>
-          <t>(전일) (휴머노이드 로봇 제조사, 8월 19일 상장) 상장 이틀 만에 차익매물로 급락</t>
+      <c r="N6" s="10" t="inlineStr">
+        <is>
+          <t>위수커지(사족보행 로봇 제조): 상장 초기 차익실현 급증, 시초가 대비 45% 넘게 반락</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -18190,19 +18554,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="8" t="inlineStr">
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>(전일) (중국 최대 컨테이너 해운사) 유럽항로 운임 급등에 해운주 강세</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -18242,10 +18606,10 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" s="8" t="inlineStr"/>
+      <c r="N8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -18296,10 +18660,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N9" s="8" t="inlineStr"/>
+      <c r="N9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -18348,14 +18712,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N10" s="8" t="inlineStr">
+      <c r="N10" s="10" t="inlineStr">
         <is>
           <t>(전일) (신재생에너지 발전 자회사) 특별한 뉴스 없음, 전력 유틸리티 업종 약세 동반</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -18402,14 +18766,14 @@
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" s="8" t="inlineStr">
+      <c r="N11" s="10" t="inlineStr">
         <is>
           <t>(전일) (금광 채굴) 미 국채금리 하락발 금값 급등에 대표 금광주로 매수 집중</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -18458,19 +18822,19 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" s="8" t="inlineStr">
+      <c r="N12" s="10" t="inlineStr">
         <is>
           <t>(전일) 상하이은행(도시상업은행): 은행·배당 ETF 자금 유입 지속, 방어주 로테이션에 사상 최고가</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -18512,15 +18876,19 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" s="8" t="inlineStr"/>
+      <c r="N13" s="10" t="inlineStr">
+        <is>
+          <t>중진황금(금 채굴): 금값 최고치 경신과 연준 인하 기대에 금광주 전반 강세</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -18568,15 +18936,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N14" s="8" t="inlineStr"/>
+      <c r="N14" s="10" t="inlineStr">
+        <is>
+          <t>웨이얼반도체(카메라용 이미지센서 설계): 알리바바 유상증자發 기술주 약세와 금리 상승 여파로 조정</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -18618,15 +18990,15 @@
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" s="8" t="inlineStr"/>
+      <c r="N15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -18666,10 +19038,14 @@
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" s="8" t="inlineStr"/>
+      <c r="N16" s="10" t="inlineStr">
+        <is>
+          <t>베리실리콘(반도체 설계자산·설계서비스): 금리 상승과 AI 밸류 부담에 반도체 설계주 동반 하락</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -18720,19 +19096,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N17" s="8" t="inlineStr">
-        <is>
-          <t>(전일) (금광 채굴기업) 금값 4,600달러선 회복에 안전자산 수요 몰려 급등</t>
+      <c r="N17" s="10" t="inlineStr">
+        <is>
+          <t>츠펑지룽금광(금 채굴): 금값 강세에도 단기 차익실현 매물에 소폭 하락</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -18776,15 +19152,19 @@
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" s="8" t="inlineStr"/>
+      <c r="N18" s="10" t="inlineStr">
+        <is>
+          <t>저장신허(비타민·정밀화학 생산): 개별 악재 미확인, 화학·성장주 동반 약세 추정</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -18830,15 +19210,15 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N19" s="8" t="inlineStr"/>
+      <c r="N19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -18882,15 +19262,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N20" s="8" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr">
+        <is>
+          <t>JLC테크놀로지(인쇄회로기판 시제품·양산): 개별 악재 미확인, 창업판 급락에 동반 하락 추정</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -18932,10 +19316,14 @@
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" s="8" t="inlineStr"/>
+      <c r="N21" s="10" t="inlineStr">
+        <is>
+          <t>산진국제금업(금 채굴): 국제 금값 사상최고, 국내 금현물 2.1% 상승에 금광주 동반 강세</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -18986,9 +19374,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N22" s="8" t="inlineStr">
-        <is>
-          <t>(전일) (정유·화학 대기업) 국제유가 한 달래 최고치 반등에 석유화학주 동반 강세</t>
+      <c r="N22" s="10" t="inlineStr">
+        <is>
+          <t>헝이석화(석유화학·폴리에스터 소재): 개별 악재 미확인, 화학 마진 우려에 급락 추정</t>
         </is>
       </c>
     </row>
